--- a/depend/ship/database.xlsx
+++ b/depend/ship/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/ship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2F7C2EE-30A8-B941-9C41-F07649CCB28E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53529017-5472-294F-8D28-CFDD9B3BE685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-35420" yWindow="1020" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6320" yWindow="500" windowWidth="29400" windowHeight="19120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="舰船数据-未改" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7453" uniqueCount="2991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7465" uniqueCount="3002">
   <si>
     <t>eid</t>
   </si>
@@ -9035,6 +9035,50 @@
   </si>
   <si>
     <t>Cid(["483","455","644"],{final_damage_buff:0.05})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BBV</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10581工程</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DD</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>休·W·哈德利</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>U</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>马伊·布雷泽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BB</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>卡拉乔洛</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>I</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -9299,122 +9343,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FF808080"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9933FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
       </font>
     </dxf>
     <dxf>
@@ -9429,42 +9363,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
       </font>
     </dxf>
     <dxf>
@@ -9474,17 +9373,17 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B0F0"/>
+        <color rgb="FFFF9900"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFC000"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -9494,42 +9393,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
+        <color rgb="FF9933FF"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
       </font>
     </dxf>
     <dxf>
@@ -9545,11 +9414,6 @@
     <dxf>
       <font>
         <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
       </font>
     </dxf>
     <dxf>
@@ -9584,6 +9448,11 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
@@ -9594,7 +9463,27 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
       </font>
     </dxf>
     <dxf>
@@ -9604,7 +9493,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9933FF"/>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
       </font>
     </dxf>
     <dxf>
@@ -9614,7 +9508,142 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
       </font>
     </dxf>
     <dxf>
@@ -9624,7 +9653,22 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF9900"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9933FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
       </font>
     </dxf>
     <dxf>
@@ -9634,7 +9678,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9933FF"/>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
@@ -9644,12 +9693,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
+        <color rgb="FF9933FF"/>
       </font>
     </dxf>
     <dxf>
@@ -9933,7 +9977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AC149"/>
+  <dimension ref="A1:AC150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="21.83203125" customWidth="1"/>
@@ -20545,7 +20589,7 @@
         <v>4</v>
       </c>
       <c r="R126" s="17">
-        <f t="shared" ref="R126:R149" si="4">SUM($S126:$V126)</f>
+        <f t="shared" ref="R126:R150" si="4">SUM($S126:$V126)</f>
         <v>9</v>
       </c>
       <c r="S126">
@@ -22444,85 +22488,169 @@
     </row>
     <row r="149" spans="1:29">
       <c r="A149" s="3">
-        <v>10640</v>
+        <v>10635</v>
       </c>
       <c r="B149" t="s">
-        <v>2063</v>
+        <v>2991</v>
       </c>
       <c r="C149" t="s">
-        <v>2179</v>
+        <v>2992</v>
       </c>
       <c r="D149" t="s">
-        <v>2011</v>
+        <v>2993</v>
       </c>
       <c r="E149">
-        <v>28</v>
+        <v>104</v>
       </c>
       <c r="F149">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="G149">
         <v>0</v>
       </c>
       <c r="H149">
-        <v>25</v>
+        <v>95</v>
       </c>
       <c r="I149">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="J149">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K149" s="1">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="L149">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="M149">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="N149">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="O149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P149">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R149" s="17">
         <f t="shared" si="4"/>
+        <v>36</v>
+      </c>
+      <c r="S149">
+        <v>9</v>
+      </c>
+      <c r="T149">
+        <v>9</v>
+      </c>
+      <c r="U149">
+        <v>9</v>
+      </c>
+      <c r="V149">
+        <v>9</v>
+      </c>
+      <c r="W149">
+        <v>170</v>
+      </c>
+      <c r="X149">
+        <v>185</v>
+      </c>
+      <c r="Y149">
+        <v>4.8</v>
+      </c>
+      <c r="Z149">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="AA149">
+        <v>106351</v>
+      </c>
+    </row>
+    <row r="150" spans="1:29">
+      <c r="A150" s="3">
+        <v>10640</v>
+      </c>
+      <c r="B150" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C150" t="s">
+        <v>2179</v>
+      </c>
+      <c r="D150" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E150">
+        <v>28</v>
+      </c>
+      <c r="F150">
+        <v>31</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>25</v>
+      </c>
+      <c r="I150">
+        <v>89</v>
+      </c>
+      <c r="J150">
+        <v>94</v>
+      </c>
+      <c r="K150" s="1">
+        <v>99</v>
+      </c>
+      <c r="L150">
+        <v>69</v>
+      </c>
+      <c r="M150">
+        <v>41</v>
+      </c>
+      <c r="N150">
+        <v>30</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="P150">
+        <v>6</v>
+      </c>
+      <c r="Q150">
+        <v>3</v>
+      </c>
+      <c r="R150" s="17">
+        <f t="shared" si="4"/>
         <v>60</v>
       </c>
-      <c r="S149">
+      <c r="S150">
         <v>20</v>
       </c>
-      <c r="T149">
+      <c r="T150">
         <v>20</v>
       </c>
-      <c r="U149">
+      <c r="U150">
         <v>20</v>
       </c>
-      <c r="V149">
-        <v>0</v>
-      </c>
-      <c r="W149">
+      <c r="V150">
+        <v>0</v>
+      </c>
+      <c r="W150">
         <v>20</v>
       </c>
-      <c r="X149">
+      <c r="X150">
         <v>40</v>
       </c>
-      <c r="Y149">
+      <c r="Y150">
         <v>0.5</v>
       </c>
-      <c r="Z149">
+      <c r="Z150">
         <v>1.1000000000000001</v>
       </c>
-      <c r="AA149">
+      <c r="AA150">
         <v>106401</v>
       </c>
     </row>
@@ -22537,40 +22665,40 @@
     <cfRule type="expression" dxfId="75" priority="7">
       <formula>F2=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="11">
-      <formula>F2=1</formula>
+    <cfRule type="expression" dxfId="74" priority="8">
+      <formula>F2=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="10">
+    <cfRule type="expression" dxfId="73" priority="9">
+      <formula>F2=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="10">
       <formula>F2=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="9">
-      <formula>F2=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="8">
-      <formula>F2=4</formula>
+    <cfRule type="expression" dxfId="71" priority="11">
+      <formula>F2=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="70" priority="12">
       <formula>F2=5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C144">
-    <cfRule type="expression" dxfId="69" priority="6">
-      <formula>F144=5</formula>
+    <cfRule type="expression" dxfId="69" priority="1">
+      <formula>F144=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="5">
+    <cfRule type="expression" dxfId="68" priority="2">
+      <formula>F144=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="3">
+      <formula>F144=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="4">
+      <formula>F144=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="5">
       <formula>F144=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="4">
-      <formula>F144=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="3">
-      <formula>F144=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="2">
-      <formula>F144=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="1">
-      <formula>F144=6</formula>
+    <cfRule type="expression" dxfId="64" priority="6">
+      <formula>F144=5</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22580,7 +22708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AC223"/>
+  <dimension ref="A1:AC226"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="3" customWidth="1"/>
@@ -22730,7 +22858,7 @@
         <v>4</v>
       </c>
       <c r="R2">
-        <f t="shared" ref="R2:R65" si="0">SUM($S2:$V2)</f>
+        <f>SUM($S2:$V2)</f>
         <v>12</v>
       </c>
       <c r="S2" s="6">
@@ -22817,7 +22945,7 @@
         <v>4</v>
       </c>
       <c r="R3">
-        <f t="shared" si="0"/>
+        <f>SUM($S3:$V3)</f>
         <v>30</v>
       </c>
       <c r="S3">
@@ -22901,7 +23029,7 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <f t="shared" si="0"/>
+        <f>SUM($S4:$V4)</f>
         <v>8</v>
       </c>
       <c r="S4" s="9">
@@ -22986,7 +23114,7 @@
         <v>4</v>
       </c>
       <c r="R5">
-        <f t="shared" si="0"/>
+        <f>SUM($S5:$V5)</f>
         <v>24</v>
       </c>
       <c r="S5">
@@ -23070,7 +23198,7 @@
         <v>4</v>
       </c>
       <c r="R6">
-        <f t="shared" si="0"/>
+        <f>SUM($S6:$V6)</f>
         <v>24</v>
       </c>
       <c r="S6">
@@ -23154,7 +23282,7 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <f t="shared" si="0"/>
+        <f>SUM($S7:$V7)</f>
         <v>16</v>
       </c>
       <c r="S7" s="9">
@@ -23241,7 +23369,7 @@
         <v>4</v>
       </c>
       <c r="R8">
-        <f t="shared" si="0"/>
+        <f>SUM($S8:$V8)</f>
         <v>16</v>
       </c>
       <c r="S8" s="9">
@@ -23326,7 +23454,7 @@
         <v>4</v>
       </c>
       <c r="R9">
-        <f t="shared" si="0"/>
+        <f>SUM($S9:$V9)</f>
         <v>0</v>
       </c>
       <c r="S9" s="9">
@@ -23414,7 +23542,7 @@
         <v>4</v>
       </c>
       <c r="R10">
-        <f t="shared" si="0"/>
+        <f>SUM($S10:$V10)</f>
         <v>8</v>
       </c>
       <c r="S10" s="9">
@@ -23504,7 +23632,7 @@
         <v>4</v>
       </c>
       <c r="R11">
-        <f t="shared" si="0"/>
+        <f>SUM($S11:$V11)</f>
         <v>16</v>
       </c>
       <c r="S11" s="9">
@@ -23591,7 +23719,7 @@
         <v>4</v>
       </c>
       <c r="R12">
-        <f t="shared" si="0"/>
+        <f>SUM($S12:$V12)</f>
         <v>12</v>
       </c>
       <c r="S12" s="9">
@@ -23676,7 +23804,7 @@
         <v>4</v>
       </c>
       <c r="R13">
-        <f t="shared" si="0"/>
+        <f>SUM($S13:$V13)</f>
         <v>12</v>
       </c>
       <c r="S13" s="9">
@@ -23761,7 +23889,7 @@
         <v>4</v>
       </c>
       <c r="R14">
-        <f t="shared" si="0"/>
+        <f>SUM($S14:$V14)</f>
         <v>12</v>
       </c>
       <c r="S14" s="9">
@@ -23846,7 +23974,7 @@
         <v>4</v>
       </c>
       <c r="R15">
-        <f t="shared" si="0"/>
+        <f>SUM($S15:$V15)</f>
         <v>12</v>
       </c>
       <c r="S15" s="9">
@@ -23931,7 +24059,7 @@
         <v>4</v>
       </c>
       <c r="R16">
-        <f t="shared" si="0"/>
+        <f>SUM($S16:$V16)</f>
         <v>16</v>
       </c>
       <c r="S16" s="6">
@@ -24018,7 +24146,7 @@
         <v>4</v>
       </c>
       <c r="R17">
-        <f t="shared" si="0"/>
+        <f>SUM($S17:$V17)</f>
         <v>16</v>
       </c>
       <c r="S17" s="6">
@@ -24103,7 +24231,7 @@
         <v>4</v>
       </c>
       <c r="R18">
-        <f t="shared" si="0"/>
+        <f>SUM($S18:$V18)</f>
         <v>48</v>
       </c>
       <c r="S18">
@@ -24187,7 +24315,7 @@
         <v>4</v>
       </c>
       <c r="R19">
-        <f t="shared" si="0"/>
+        <f>SUM($S19:$V19)</f>
         <v>48</v>
       </c>
       <c r="S19">
@@ -24271,7 +24399,7 @@
         <v>4</v>
       </c>
       <c r="R20">
-        <f t="shared" si="0"/>
+        <f>SUM($S20:$V20)</f>
         <v>86</v>
       </c>
       <c r="S20">
@@ -24358,7 +24486,7 @@
         <v>4</v>
       </c>
       <c r="R21">
-        <f t="shared" si="0"/>
+        <f>SUM($S21:$V21)</f>
         <v>95</v>
       </c>
       <c r="S21">
@@ -24445,7 +24573,7 @@
         <v>3</v>
       </c>
       <c r="R22">
-        <f t="shared" si="0"/>
+        <f>SUM($S22:$V22)</f>
         <v>39</v>
       </c>
       <c r="S22">
@@ -24529,7 +24657,7 @@
         <v>3</v>
       </c>
       <c r="R23">
-        <f t="shared" si="0"/>
+        <f>SUM($S23:$V23)</f>
         <v>37</v>
       </c>
       <c r="S23">
@@ -24613,7 +24741,7 @@
         <v>3</v>
       </c>
       <c r="R24">
-        <f t="shared" si="0"/>
+        <f>SUM($S24:$V24)</f>
         <v>28</v>
       </c>
       <c r="S24">
@@ -24694,7 +24822,7 @@
         <v>3</v>
       </c>
       <c r="R25">
-        <f t="shared" si="0"/>
+        <f>SUM($S25:$V25)</f>
         <v>35</v>
       </c>
       <c r="S25">
@@ -24775,7 +24903,7 @@
         <v>4</v>
       </c>
       <c r="R26">
-        <f t="shared" si="0"/>
+        <f>SUM($S26:$V26)</f>
         <v>65</v>
       </c>
       <c r="S26">
@@ -24859,7 +24987,7 @@
         <v>4</v>
       </c>
       <c r="R27">
-        <f t="shared" si="0"/>
+        <f>SUM($S27:$V27)</f>
         <v>85</v>
       </c>
       <c r="S27">
@@ -24943,7 +25071,7 @@
         <v>4</v>
       </c>
       <c r="R28">
-        <f t="shared" si="0"/>
+        <f>SUM($S28:$V28)</f>
         <v>85</v>
       </c>
       <c r="S28">
@@ -25030,7 +25158,7 @@
         <v>4</v>
       </c>
       <c r="R29">
-        <f t="shared" si="0"/>
+        <f>SUM($S29:$V29)</f>
         <v>87</v>
       </c>
       <c r="S29">
@@ -25114,7 +25242,7 @@
         <v>4</v>
       </c>
       <c r="R30">
-        <f t="shared" si="0"/>
+        <f>SUM($S30:$V30)</f>
         <v>6</v>
       </c>
       <c r="S30" s="6">
@@ -25199,7 +25327,7 @@
         <v>4</v>
       </c>
       <c r="R31">
-        <f t="shared" si="0"/>
+        <f>SUM($S31:$V31)</f>
         <v>6</v>
       </c>
       <c r="S31" s="6">
@@ -25284,7 +25412,7 @@
         <v>4</v>
       </c>
       <c r="R32">
-        <f t="shared" si="0"/>
+        <f>SUM($S32:$V32)</f>
         <v>6</v>
       </c>
       <c r="S32" s="6">
@@ -25369,7 +25497,7 @@
         <v>4</v>
       </c>
       <c r="R33">
-        <f t="shared" si="0"/>
+        <f>SUM($S33:$V33)</f>
         <v>6</v>
       </c>
       <c r="S33" s="6">
@@ -25454,7 +25582,7 @@
         <v>4</v>
       </c>
       <c r="R34">
-        <f t="shared" si="0"/>
+        <f>SUM($S34:$V34)</f>
         <v>12</v>
       </c>
       <c r="S34" s="6">
@@ -25539,7 +25667,7 @@
         <v>4</v>
       </c>
       <c r="R35">
-        <f t="shared" si="0"/>
+        <f>SUM($S35:$V35)</f>
         <v>12</v>
       </c>
       <c r="S35" s="6">
@@ -25624,7 +25752,7 @@
         <v>4</v>
       </c>
       <c r="R36">
-        <f t="shared" si="0"/>
+        <f>SUM($S36:$V36)</f>
         <v>12</v>
       </c>
       <c r="S36" s="6">
@@ -25711,7 +25839,7 @@
         <v>4</v>
       </c>
       <c r="R37">
-        <f t="shared" si="0"/>
+        <f>SUM($S37:$V37)</f>
         <v>6</v>
       </c>
       <c r="S37" s="6">
@@ -25796,7 +25924,7 @@
         <v>4</v>
       </c>
       <c r="R38">
-        <f t="shared" si="0"/>
+        <f>SUM($S38:$V38)</f>
         <v>8</v>
       </c>
       <c r="S38" s="6">
@@ -25883,7 +26011,7 @@
         <v>3</v>
       </c>
       <c r="R39" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S39:$V39)</f>
         <v>0</v>
       </c>
       <c r="S39">
@@ -25970,7 +26098,7 @@
         <v>3</v>
       </c>
       <c r="R40" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S40:$V40)</f>
         <v>0</v>
       </c>
       <c r="S40">
@@ -26057,7 +26185,7 @@
         <v>3</v>
       </c>
       <c r="R41" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S41:$V41)</f>
         <v>3</v>
       </c>
       <c r="S41">
@@ -26141,7 +26269,7 @@
         <v>4</v>
       </c>
       <c r="R42" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S42:$V42)</f>
         <v>0</v>
       </c>
       <c r="S42">
@@ -26225,7 +26353,7 @@
         <v>3</v>
       </c>
       <c r="R43">
-        <f t="shared" si="0"/>
+        <f>SUM($S43:$V43)</f>
         <v>0</v>
       </c>
       <c r="S43" s="6">
@@ -26310,7 +26438,7 @@
         <v>3</v>
       </c>
       <c r="R44">
-        <f t="shared" si="0"/>
+        <f>SUM($S44:$V44)</f>
         <v>6</v>
       </c>
       <c r="S44" s="6">
@@ -26395,7 +26523,7 @@
         <v>3</v>
       </c>
       <c r="R45">
-        <f t="shared" si="0"/>
+        <f>SUM($S45:$V45)</f>
         <v>0</v>
       </c>
       <c r="S45" s="6">
@@ -26483,7 +26611,7 @@
         <v>3</v>
       </c>
       <c r="R46">
-        <f t="shared" si="0"/>
+        <f>SUM($S46:$V46)</f>
         <v>0</v>
       </c>
       <c r="S46" s="6">
@@ -26571,7 +26699,7 @@
         <v>3</v>
       </c>
       <c r="R47">
-        <f t="shared" si="0"/>
+        <f>SUM($S47:$V47)</f>
         <v>12</v>
       </c>
       <c r="S47" s="6">
@@ -26658,7 +26786,7 @@
         <v>3</v>
       </c>
       <c r="R48" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S48:$V48)</f>
         <v>0</v>
       </c>
       <c r="S48">
@@ -26742,7 +26870,7 @@
         <v>3</v>
       </c>
       <c r="R49" s="17">
-        <f t="shared" si="0"/>
+        <f>SUM($S49:$V49)</f>
         <v>0</v>
       </c>
       <c r="S49">
@@ -26826,7 +26954,7 @@
         <v>3</v>
       </c>
       <c r="R50">
-        <f t="shared" si="0"/>
+        <f>SUM($S50:$V50)</f>
         <v>0</v>
       </c>
       <c r="S50" s="6">
@@ -26916,7 +27044,7 @@
         <v>3</v>
       </c>
       <c r="R51">
-        <f t="shared" si="0"/>
+        <f>SUM($S51:$V51)</f>
         <v>0</v>
       </c>
       <c r="S51" s="6">
@@ -27004,7 +27132,7 @@
         <v>3</v>
       </c>
       <c r="R52">
-        <f t="shared" si="0"/>
+        <f>SUM($S52:$V52)</f>
         <v>0</v>
       </c>
       <c r="S52" s="6">
@@ -27092,7 +27220,7 @@
         <v>3</v>
       </c>
       <c r="R53">
-        <f t="shared" si="0"/>
+        <f>SUM($S53:$V53)</f>
         <v>0</v>
       </c>
       <c r="S53" s="6">
@@ -27180,7 +27308,7 @@
         <v>3</v>
       </c>
       <c r="R54">
-        <f t="shared" si="0"/>
+        <f>SUM($S54:$V54)</f>
         <v>0</v>
       </c>
       <c r="S54" s="6">
@@ -27268,7 +27396,7 @@
         <v>3</v>
       </c>
       <c r="R55">
-        <f t="shared" si="0"/>
+        <f>SUM($S55:$V55)</f>
         <v>0</v>
       </c>
       <c r="S55" s="6">
@@ -27356,7 +27484,7 @@
         <v>3</v>
       </c>
       <c r="R56">
-        <f t="shared" si="0"/>
+        <f>SUM($S56:$V56)</f>
         <v>0</v>
       </c>
       <c r="S56" s="6">
@@ -27444,7 +27572,7 @@
         <v>3</v>
       </c>
       <c r="R57">
-        <f t="shared" si="0"/>
+        <f>SUM($S57:$V57)</f>
         <v>0</v>
       </c>
       <c r="S57" s="6">
@@ -27532,7 +27660,7 @@
         <v>3</v>
       </c>
       <c r="R58">
-        <f t="shared" si="0"/>
+        <f>SUM($S58:$V58)</f>
         <v>0</v>
       </c>
       <c r="S58" s="6">
@@ -27620,7 +27748,7 @@
         <v>3</v>
       </c>
       <c r="R59">
-        <f t="shared" si="0"/>
+        <f>SUM($S59:$V59)</f>
         <v>0</v>
       </c>
       <c r="S59" s="6">
@@ -27708,7 +27836,7 @@
         <v>3</v>
       </c>
       <c r="R60">
-        <f t="shared" si="0"/>
+        <f>SUM($S60:$V60)</f>
         <v>0</v>
       </c>
       <c r="S60" s="6">
@@ -27796,7 +27924,7 @@
         <v>3</v>
       </c>
       <c r="R61">
-        <f t="shared" si="0"/>
+        <f>SUM($S61:$V61)</f>
         <v>0</v>
       </c>
       <c r="S61" s="6">
@@ -27886,7 +28014,7 @@
         <v>3</v>
       </c>
       <c r="R62">
-        <f t="shared" si="0"/>
+        <f>SUM($S62:$V62)</f>
         <v>0</v>
       </c>
       <c r="S62" s="6">
@@ -27974,7 +28102,7 @@
         <v>3</v>
       </c>
       <c r="R63">
-        <f t="shared" si="0"/>
+        <f>SUM($S63:$V63)</f>
         <v>0</v>
       </c>
       <c r="S63" s="6">
@@ -28062,7 +28190,7 @@
         <v>3</v>
       </c>
       <c r="R64">
-        <f t="shared" si="0"/>
+        <f>SUM($S64:$V64)</f>
         <v>0</v>
       </c>
       <c r="S64" s="6">
@@ -28150,7 +28278,7 @@
         <v>3</v>
       </c>
       <c r="R65">
-        <f t="shared" si="0"/>
+        <f>SUM($S65:$V65)</f>
         <v>0</v>
       </c>
       <c r="S65" s="6">
@@ -28238,7 +28366,7 @@
         <v>3</v>
       </c>
       <c r="R66">
-        <f t="shared" ref="R66:R129" si="1">SUM($S66:$V66)</f>
+        <f>SUM($S66:$V66)</f>
         <v>0</v>
       </c>
       <c r="S66" s="6">
@@ -28323,7 +28451,7 @@
         <v>3</v>
       </c>
       <c r="R67">
-        <f t="shared" si="1"/>
+        <f>SUM($S67:$V67)</f>
         <v>0</v>
       </c>
       <c r="S67" s="6">
@@ -28410,7 +28538,7 @@
         <v>3</v>
       </c>
       <c r="R68">
-        <f t="shared" si="1"/>
+        <f>SUM($S68:$V68)</f>
         <v>0</v>
       </c>
       <c r="S68" s="6">
@@ -28495,7 +28623,7 @@
         <v>3</v>
       </c>
       <c r="R69">
-        <f t="shared" si="1"/>
+        <f>SUM($S69:$V69)</f>
         <v>0</v>
       </c>
       <c r="S69" s="6">
@@ -28580,7 +28708,7 @@
         <v>3</v>
       </c>
       <c r="R70">
-        <f t="shared" si="1"/>
+        <f>SUM($S70:$V70)</f>
         <v>0</v>
       </c>
       <c r="S70" s="6">
@@ -28665,7 +28793,7 @@
         <v>3</v>
       </c>
       <c r="R71">
-        <f t="shared" si="1"/>
+        <f>SUM($S71:$V71)</f>
         <v>0</v>
       </c>
       <c r="S71" s="6">
@@ -28750,7 +28878,7 @@
         <v>3</v>
       </c>
       <c r="R72">
-        <f t="shared" si="1"/>
+        <f>SUM($S72:$V72)</f>
         <v>0</v>
       </c>
       <c r="S72" s="6">
@@ -28835,7 +28963,7 @@
         <v>3</v>
       </c>
       <c r="R73">
-        <f t="shared" si="1"/>
+        <f>SUM($S73:$V73)</f>
         <v>0</v>
       </c>
       <c r="S73" s="6">
@@ -28920,7 +29048,7 @@
         <v>3</v>
       </c>
       <c r="R74">
-        <f t="shared" si="1"/>
+        <f>SUM($S74:$V74)</f>
         <v>0</v>
       </c>
       <c r="S74" s="6">
@@ -29005,7 +29133,7 @@
         <v>3</v>
       </c>
       <c r="R75">
-        <f t="shared" si="1"/>
+        <f>SUM($S75:$V75)</f>
         <v>0</v>
       </c>
       <c r="S75" s="6">
@@ -29090,7 +29218,7 @@
         <v>3</v>
       </c>
       <c r="R76">
-        <f t="shared" si="1"/>
+        <f>SUM($S76:$V76)</f>
         <v>0</v>
       </c>
       <c r="S76" s="6">
@@ -29177,7 +29305,7 @@
         <v>3</v>
       </c>
       <c r="R77">
-        <f t="shared" si="1"/>
+        <f>SUM($S77:$V77)</f>
         <v>36</v>
       </c>
       <c r="S77">
@@ -29262,7 +29390,7 @@
         <v>3</v>
       </c>
       <c r="R78">
-        <f t="shared" si="1"/>
+        <f>SUM($S78:$V78)</f>
         <v>24</v>
       </c>
       <c r="S78">
@@ -29350,7 +29478,7 @@
         <v>3</v>
       </c>
       <c r="R79">
-        <f t="shared" si="1"/>
+        <f>SUM($S79:$V79)</f>
         <v>0</v>
       </c>
       <c r="S79" s="6">
@@ -29435,7 +29563,7 @@
         <v>3</v>
       </c>
       <c r="R80">
-        <f t="shared" si="1"/>
+        <f>SUM($S80:$V80)</f>
         <v>0</v>
       </c>
       <c r="S80" s="6">
@@ -29520,7 +29648,7 @@
         <v>4</v>
       </c>
       <c r="R81">
-        <f t="shared" si="1"/>
+        <f>SUM($S81:$V81)</f>
         <v>0</v>
       </c>
       <c r="S81" s="9">
@@ -29610,7 +29738,7 @@
         <v>4</v>
       </c>
       <c r="R82">
-        <f t="shared" si="1"/>
+        <f>SUM($S82:$V82)</f>
         <v>12</v>
       </c>
       <c r="S82" s="9">
@@ -29700,7 +29828,7 @@
         <v>4</v>
       </c>
       <c r="R83">
-        <f t="shared" si="1"/>
+        <f>SUM($S83:$V83)</f>
         <v>12</v>
       </c>
       <c r="S83" s="9">
@@ -29790,7 +29918,7 @@
         <v>4</v>
       </c>
       <c r="R84">
-        <f t="shared" si="1"/>
+        <f>SUM($S84:$V84)</f>
         <v>12</v>
       </c>
       <c r="S84" s="9">
@@ -29877,7 +30005,7 @@
         <v>4</v>
       </c>
       <c r="R85">
-        <f t="shared" si="1"/>
+        <f>SUM($S85:$V85)</f>
         <v>16</v>
       </c>
       <c r="S85" s="9">
@@ -29962,7 +30090,7 @@
         <v>4</v>
       </c>
       <c r="R86">
-        <f t="shared" si="1"/>
+        <f>SUM($S86:$V86)</f>
         <v>16</v>
       </c>
       <c r="S86" s="9">
@@ -30047,7 +30175,7 @@
         <v>4</v>
       </c>
       <c r="R87">
-        <f t="shared" si="1"/>
+        <f>SUM($S87:$V87)</f>
         <v>16</v>
       </c>
       <c r="S87" s="9">
@@ -30135,7 +30263,7 @@
         <v>4</v>
       </c>
       <c r="R88">
-        <f t="shared" si="1"/>
+        <f>SUM($S88:$V88)</f>
         <v>16</v>
       </c>
       <c r="S88" s="9">
@@ -30225,7 +30353,7 @@
         <v>4</v>
       </c>
       <c r="R89">
-        <f t="shared" si="1"/>
+        <f>SUM($S89:$V89)</f>
         <v>12</v>
       </c>
       <c r="S89" s="9">
@@ -30315,7 +30443,7 @@
         <v>4</v>
       </c>
       <c r="R90">
-        <f t="shared" si="1"/>
+        <f>SUM($S90:$V90)</f>
         <v>12</v>
       </c>
       <c r="S90" s="9">
@@ -30402,7 +30530,7 @@
         <v>4</v>
       </c>
       <c r="R91">
-        <f t="shared" si="1"/>
+        <f>SUM($S91:$V91)</f>
         <v>12</v>
       </c>
       <c r="S91" s="9">
@@ -30490,7 +30618,7 @@
         <v>4</v>
       </c>
       <c r="R92">
-        <f t="shared" si="1"/>
+        <f>SUM($S92:$V92)</f>
         <v>0</v>
       </c>
       <c r="S92" s="9">
@@ -30577,7 +30705,7 @@
         <v>4</v>
       </c>
       <c r="R93">
-        <f t="shared" si="1"/>
+        <f>SUM($S93:$V93)</f>
         <v>72</v>
       </c>
       <c r="S93">
@@ -30664,7 +30792,7 @@
         <v>4</v>
       </c>
       <c r="R94">
-        <f t="shared" si="1"/>
+        <f>SUM($S94:$V94)</f>
         <v>68</v>
       </c>
       <c r="S94">
@@ -30749,7 +30877,7 @@
         <v>4</v>
       </c>
       <c r="R95">
-        <f t="shared" si="1"/>
+        <f>SUM($S95:$V95)</f>
         <v>83</v>
       </c>
       <c r="S95">
@@ -30834,7 +30962,7 @@
         <v>4</v>
       </c>
       <c r="R96">
-        <f t="shared" si="1"/>
+        <f>SUM($S96:$V96)</f>
         <v>90</v>
       </c>
       <c r="S96">
@@ -30921,7 +31049,7 @@
         <v>3</v>
       </c>
       <c r="R97">
-        <f t="shared" si="1"/>
+        <f>SUM($S97:$V97)</f>
         <v>32</v>
       </c>
       <c r="S97">
@@ -31006,7 +31134,7 @@
         <v>3</v>
       </c>
       <c r="R98">
-        <f t="shared" si="1"/>
+        <f>SUM($S98:$V98)</f>
         <v>32</v>
       </c>
       <c r="S98">
@@ -31091,7 +31219,7 @@
         <v>3</v>
       </c>
       <c r="R99">
-        <f t="shared" si="1"/>
+        <f>SUM($S99:$V99)</f>
         <v>46</v>
       </c>
       <c r="S99">
@@ -31176,7 +31304,7 @@
         <v>3</v>
       </c>
       <c r="R100">
-        <f t="shared" si="1"/>
+        <f>SUM($S100:$V100)</f>
         <v>39</v>
       </c>
       <c r="S100">
@@ -31261,7 +31389,7 @@
         <v>4</v>
       </c>
       <c r="R101">
-        <f t="shared" si="1"/>
+        <f>SUM($S101:$V101)</f>
         <v>6</v>
       </c>
       <c r="S101" s="6">
@@ -31348,7 +31476,7 @@
         <v>4</v>
       </c>
       <c r="R102">
-        <f t="shared" si="1"/>
+        <f>SUM($S102:$V102)</f>
         <v>6</v>
       </c>
       <c r="S102" s="6">
@@ -31433,7 +31561,7 @@
         <v>4</v>
       </c>
       <c r="R103">
-        <f t="shared" si="1"/>
+        <f>SUM($S103:$V103)</f>
         <v>8</v>
       </c>
       <c r="S103" s="6">
@@ -31518,7 +31646,7 @@
         <v>4</v>
       </c>
       <c r="R104">
-        <f t="shared" si="1"/>
+        <f>SUM($S104:$V104)</f>
         <v>6</v>
       </c>
       <c r="S104" s="6">
@@ -31603,7 +31731,7 @@
         <v>4</v>
       </c>
       <c r="R105">
-        <f t="shared" si="1"/>
+        <f>SUM($S105:$V105)</f>
         <v>0</v>
       </c>
       <c r="S105" s="6">
@@ -31688,7 +31816,7 @@
         <v>4</v>
       </c>
       <c r="R106">
-        <f t="shared" si="1"/>
+        <f>SUM($S106:$V106)</f>
         <v>0</v>
       </c>
       <c r="S106" s="6">
@@ -31773,7 +31901,7 @@
         <v>4</v>
       </c>
       <c r="R107">
-        <f t="shared" si="1"/>
+        <f>SUM($S107:$V107)</f>
         <v>0</v>
       </c>
       <c r="S107" s="6">
@@ -31858,7 +31986,7 @@
         <v>4</v>
       </c>
       <c r="R108">
-        <f t="shared" si="1"/>
+        <f>SUM($S108:$V108)</f>
         <v>8</v>
       </c>
       <c r="S108" s="6">
@@ -31943,7 +32071,7 @@
         <v>4</v>
       </c>
       <c r="R109">
-        <f t="shared" si="1"/>
+        <f>SUM($S109:$V109)</f>
         <v>0</v>
       </c>
       <c r="S109" s="6">
@@ -32028,7 +32156,7 @@
         <v>4</v>
       </c>
       <c r="R110">
-        <f t="shared" si="1"/>
+        <f>SUM($S110:$V110)</f>
         <v>0</v>
       </c>
       <c r="S110" s="6">
@@ -32113,7 +32241,7 @@
         <v>4</v>
       </c>
       <c r="R111">
-        <f t="shared" si="1"/>
+        <f>SUM($S111:$V111)</f>
         <v>0</v>
       </c>
       <c r="S111" s="6">
@@ -32198,7 +32326,7 @@
         <v>3</v>
       </c>
       <c r="R112" s="17">
-        <f t="shared" si="1"/>
+        <f>SUM($S112:$V112)</f>
         <v>0</v>
       </c>
       <c r="S112">
@@ -32285,7 +32413,7 @@
         <v>3</v>
       </c>
       <c r="R113">
-        <f t="shared" si="1"/>
+        <f>SUM($S113:$V113)</f>
         <v>6</v>
       </c>
       <c r="S113" s="6">
@@ -32370,7 +32498,7 @@
         <v>3</v>
       </c>
       <c r="R114">
-        <f t="shared" si="1"/>
+        <f>SUM($S114:$V114)</f>
         <v>0</v>
       </c>
       <c r="S114" s="6">
@@ -32455,7 +32583,7 @@
         <v>3</v>
       </c>
       <c r="R115">
-        <f t="shared" si="1"/>
+        <f>SUM($S115:$V115)</f>
         <v>0</v>
       </c>
       <c r="S115" s="6">
@@ -32540,7 +32668,7 @@
         <v>3</v>
       </c>
       <c r="R116">
-        <f t="shared" si="1"/>
+        <f>SUM($S116:$V116)</f>
         <v>0</v>
       </c>
       <c r="S116" s="6">
@@ -32625,7 +32753,7 @@
         <v>3</v>
       </c>
       <c r="R117">
-        <f t="shared" si="1"/>
+        <f>SUM($S117:$V117)</f>
         <v>0</v>
       </c>
       <c r="S117" s="6">
@@ -32710,7 +32838,7 @@
         <v>3</v>
       </c>
       <c r="R118">
-        <f t="shared" si="1"/>
+        <f>SUM($S118:$V118)</f>
         <v>0</v>
       </c>
       <c r="S118" s="6">
@@ -32795,7 +32923,7 @@
         <v>3</v>
       </c>
       <c r="R119">
-        <f t="shared" si="1"/>
+        <f>SUM($S119:$V119)</f>
         <v>0</v>
       </c>
       <c r="S119" s="6">
@@ -32880,7 +33008,7 @@
         <v>3</v>
       </c>
       <c r="R120">
-        <f t="shared" si="1"/>
+        <f>SUM($S120:$V120)</f>
         <v>0</v>
       </c>
       <c r="S120" s="6">
@@ -32967,7 +33095,7 @@
         <v>3</v>
       </c>
       <c r="R121">
-        <f t="shared" si="1"/>
+        <f>SUM($S121:$V121)</f>
         <v>0</v>
       </c>
       <c r="S121" s="6">
@@ -33055,7 +33183,7 @@
         <v>3</v>
       </c>
       <c r="R122">
-        <f t="shared" si="1"/>
+        <f>SUM($S122:$V122)</f>
         <v>0</v>
       </c>
       <c r="S122" s="6">
@@ -33140,7 +33268,7 @@
         <v>3</v>
       </c>
       <c r="R123">
-        <f t="shared" si="1"/>
+        <f>SUM($S123:$V123)</f>
         <v>0</v>
       </c>
       <c r="S123" s="6">
@@ -33225,7 +33353,7 @@
         <v>3</v>
       </c>
       <c r="R124">
-        <f t="shared" si="1"/>
+        <f>SUM($S124:$V124)</f>
         <v>0</v>
       </c>
       <c r="S124" s="6">
@@ -33312,7 +33440,7 @@
         <v>3</v>
       </c>
       <c r="R125">
-        <f t="shared" si="1"/>
+        <f>SUM($S125:$V125)</f>
         <v>0</v>
       </c>
       <c r="S125" s="6">
@@ -33397,7 +33525,7 @@
         <v>3</v>
       </c>
       <c r="R126">
-        <f t="shared" si="1"/>
+        <f>SUM($S126:$V126)</f>
         <v>0</v>
       </c>
       <c r="S126" s="6">
@@ -33482,7 +33610,7 @@
         <v>3</v>
       </c>
       <c r="R127">
-        <f t="shared" si="1"/>
+        <f>SUM($S127:$V127)</f>
         <v>0</v>
       </c>
       <c r="S127" s="6">
@@ -33567,7 +33695,7 @@
         <v>3</v>
       </c>
       <c r="R128">
-        <f t="shared" si="1"/>
+        <f>SUM($S128:$V128)</f>
         <v>0</v>
       </c>
       <c r="S128" s="6">
@@ -33652,7 +33780,7 @@
         <v>3</v>
       </c>
       <c r="R129">
-        <f t="shared" si="1"/>
+        <f>SUM($S129:$V129)</f>
         <v>0</v>
       </c>
       <c r="S129" s="6">
@@ -33737,7 +33865,7 @@
         <v>3</v>
       </c>
       <c r="R130">
-        <f t="shared" ref="R130:R193" si="2">SUM($S130:$V130)</f>
+        <f>SUM($S130:$V130)</f>
         <v>0</v>
       </c>
       <c r="S130" s="6">
@@ -33822,7 +33950,7 @@
         <v>3</v>
       </c>
       <c r="R131">
-        <f t="shared" si="2"/>
+        <f>SUM($S131:$V131)</f>
         <v>0</v>
       </c>
       <c r="S131" s="17">
@@ -33907,7 +34035,7 @@
         <v>3</v>
       </c>
       <c r="R132">
-        <f t="shared" si="2"/>
+        <f>SUM($S132:$V132)</f>
         <v>0</v>
       </c>
       <c r="S132" s="17">
@@ -33992,7 +34120,7 @@
         <v>3</v>
       </c>
       <c r="R133">
-        <f t="shared" si="2"/>
+        <f>SUM($S133:$V133)</f>
         <v>0</v>
       </c>
       <c r="S133" s="17">
@@ -34082,7 +34210,7 @@
         <v>3</v>
       </c>
       <c r="R134" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S134:$V134)</f>
         <v>0</v>
       </c>
       <c r="S134">
@@ -34169,7 +34297,7 @@
         <v>3</v>
       </c>
       <c r="R135">
-        <f t="shared" si="2"/>
+        <f>SUM($S135:$V135)</f>
         <v>0</v>
       </c>
       <c r="S135">
@@ -34254,7 +34382,7 @@
         <v>4</v>
       </c>
       <c r="R136" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S136:$V136)</f>
         <v>8</v>
       </c>
       <c r="S136">
@@ -34341,7 +34469,7 @@
         <v>4</v>
       </c>
       <c r="R137">
-        <f t="shared" si="2"/>
+        <f>SUM($S137:$V137)</f>
         <v>0</v>
       </c>
       <c r="S137" s="9">
@@ -34428,7 +34556,7 @@
         <v>4</v>
       </c>
       <c r="R138">
-        <f t="shared" si="2"/>
+        <f>SUM($S138:$V138)</f>
         <v>12</v>
       </c>
       <c r="S138" s="9">
@@ -34518,7 +34646,7 @@
         <v>4</v>
       </c>
       <c r="R139">
-        <f t="shared" si="2"/>
+        <f>SUM($S139:$V139)</f>
         <v>32</v>
       </c>
       <c r="S139">
@@ -34608,7 +34736,7 @@
         <v>4</v>
       </c>
       <c r="R140">
-        <f t="shared" si="2"/>
+        <f>SUM($S140:$V140)</f>
         <v>12</v>
       </c>
       <c r="S140" s="9">
@@ -34693,7 +34821,7 @@
         <v>4</v>
       </c>
       <c r="R141" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S141:$V141)</f>
         <v>0</v>
       </c>
       <c r="S141">
@@ -34777,7 +34905,7 @@
         <v>4</v>
       </c>
       <c r="R142">
-        <f t="shared" si="2"/>
+        <f>SUM($S142:$V142)</f>
         <v>87</v>
       </c>
       <c r="S142">
@@ -34862,7 +34990,7 @@
         <v>4</v>
       </c>
       <c r="R143">
-        <f t="shared" si="2"/>
+        <f>SUM($S143:$V143)</f>
         <v>87</v>
       </c>
       <c r="S143">
@@ -34947,7 +35075,7 @@
         <v>4</v>
       </c>
       <c r="R144">
-        <f t="shared" si="2"/>
+        <f>SUM($S144:$V144)</f>
         <v>73</v>
       </c>
       <c r="S144">
@@ -35034,7 +35162,7 @@
         <v>4</v>
       </c>
       <c r="R145">
-        <f t="shared" si="2"/>
+        <f>SUM($S145:$V145)</f>
         <v>70</v>
       </c>
       <c r="S145">
@@ -35119,7 +35247,7 @@
         <v>4</v>
       </c>
       <c r="R146">
-        <f t="shared" si="2"/>
+        <f>SUM($S146:$V146)</f>
         <v>72</v>
       </c>
       <c r="S146">
@@ -35206,7 +35334,7 @@
         <v>4</v>
       </c>
       <c r="R147">
-        <f t="shared" si="2"/>
+        <f>SUM($S147:$V147)</f>
         <v>69</v>
       </c>
       <c r="S147">
@@ -35293,7 +35421,7 @@
         <v>4</v>
       </c>
       <c r="R148">
-        <f t="shared" si="2"/>
+        <f>SUM($S148:$V148)</f>
         <v>82</v>
       </c>
       <c r="S148">
@@ -35378,7 +35506,7 @@
         <v>3</v>
       </c>
       <c r="R149">
-        <f t="shared" si="2"/>
+        <f>SUM($S149:$V149)</f>
         <v>55</v>
       </c>
       <c r="S149">
@@ -35463,7 +35591,7 @@
         <v>3</v>
       </c>
       <c r="R150">
-        <f t="shared" si="2"/>
+        <f>SUM($S150:$V150)</f>
         <v>55</v>
       </c>
       <c r="S150">
@@ -35548,7 +35676,7 @@
         <v>4</v>
       </c>
       <c r="R151" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S151:$V151)</f>
         <v>56</v>
       </c>
       <c r="S151">
@@ -35632,7 +35760,7 @@
         <v>4</v>
       </c>
       <c r="R152">
-        <f t="shared" si="2"/>
+        <f>SUM($S152:$V152)</f>
         <v>12</v>
       </c>
       <c r="S152" s="6">
@@ -35717,7 +35845,7 @@
         <v>4</v>
       </c>
       <c r="R153" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S153:$V153)</f>
         <v>8</v>
       </c>
       <c r="S153">
@@ -35801,7 +35929,7 @@
         <v>4</v>
       </c>
       <c r="R154" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S154:$V154)</f>
         <v>8</v>
       </c>
       <c r="S154">
@@ -35885,7 +36013,7 @@
         <v>4</v>
       </c>
       <c r="R155">
-        <f t="shared" si="2"/>
+        <f>SUM($S155:$V155)</f>
         <v>8</v>
       </c>
       <c r="S155" s="6">
@@ -35970,7 +36098,7 @@
         <v>4</v>
       </c>
       <c r="R156">
-        <f t="shared" si="2"/>
+        <f>SUM($S156:$V156)</f>
         <v>8</v>
       </c>
       <c r="S156" s="6">
@@ -36057,7 +36185,7 @@
         <v>3</v>
       </c>
       <c r="R157" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S157:$V157)</f>
         <v>0</v>
       </c>
       <c r="S157">
@@ -36141,7 +36269,7 @@
         <v>4</v>
       </c>
       <c r="R158">
-        <f t="shared" si="2"/>
+        <f>SUM($S158:$V158)</f>
         <v>18</v>
       </c>
       <c r="S158" s="6">
@@ -36226,7 +36354,7 @@
         <v>3</v>
       </c>
       <c r="R159" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S159:$V159)</f>
         <v>0</v>
       </c>
       <c r="S159">
@@ -36310,7 +36438,7 @@
         <v>3</v>
       </c>
       <c r="R160">
-        <f t="shared" si="2"/>
+        <f>SUM($S160:$V160)</f>
         <v>0</v>
       </c>
       <c r="S160" s="6">
@@ -36395,7 +36523,7 @@
         <v>3</v>
       </c>
       <c r="R161" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S161:$V161)</f>
         <v>0</v>
       </c>
       <c r="S161">
@@ -36482,7 +36610,7 @@
         <v>3</v>
       </c>
       <c r="R162" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S162:$V162)</f>
         <v>0</v>
       </c>
       <c r="S162">
@@ -36566,7 +36694,7 @@
         <v>3</v>
       </c>
       <c r="R163">
-        <f t="shared" si="2"/>
+        <f>SUM($S163:$V163)</f>
         <v>0</v>
       </c>
       <c r="S163" s="6">
@@ -36654,7 +36782,7 @@
         <v>3</v>
       </c>
       <c r="R164">
-        <f t="shared" si="2"/>
+        <f>SUM($S164:$V164)</f>
         <v>0</v>
       </c>
       <c r="S164" s="6">
@@ -36742,7 +36870,7 @@
         <v>3</v>
       </c>
       <c r="R165" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S165:$V165)</f>
         <v>0</v>
       </c>
       <c r="S165">
@@ -36826,7 +36954,7 @@
         <v>3</v>
       </c>
       <c r="R166" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S166:$V166)</f>
         <v>0</v>
       </c>
       <c r="S166">
@@ -36913,7 +37041,7 @@
         <v>3</v>
       </c>
       <c r="R167" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S167:$V167)</f>
         <v>0</v>
       </c>
       <c r="S167">
@@ -37000,7 +37128,7 @@
         <v>3</v>
       </c>
       <c r="R168">
-        <f t="shared" si="2"/>
+        <f>SUM($S168:$V168)</f>
         <v>0</v>
       </c>
       <c r="S168" s="6">
@@ -37087,7 +37215,7 @@
         <v>3</v>
       </c>
       <c r="R169">
-        <f t="shared" si="2"/>
+        <f>SUM($S169:$V169)</f>
         <v>0</v>
       </c>
       <c r="S169" s="6">
@@ -37174,7 +37302,7 @@
         <v>3</v>
       </c>
       <c r="R170">
-        <f t="shared" si="2"/>
+        <f>SUM($S170:$V170)</f>
         <v>0</v>
       </c>
       <c r="S170" s="6">
@@ -37261,7 +37389,7 @@
         <v>3</v>
       </c>
       <c r="R171">
-        <f t="shared" si="2"/>
+        <f>SUM($S171:$V171)</f>
         <v>0</v>
       </c>
       <c r="S171" s="17">
@@ -37348,7 +37476,7 @@
         <v>3</v>
       </c>
       <c r="R172">
-        <f t="shared" si="2"/>
+        <f>SUM($S172:$V172)</f>
         <v>0</v>
       </c>
       <c r="S172" s="17">
@@ -37435,7 +37563,7 @@
         <v>3</v>
       </c>
       <c r="R173" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S173:$V173)</f>
         <v>0</v>
       </c>
       <c r="S173">
@@ -37522,7 +37650,7 @@
         <v>3</v>
       </c>
       <c r="R174">
-        <f t="shared" si="2"/>
+        <f>SUM($S174:$V174)</f>
         <v>0</v>
       </c>
       <c r="S174" s="17">
@@ -37609,7 +37737,7 @@
         <v>4</v>
       </c>
       <c r="R175">
-        <f t="shared" si="2"/>
+        <f>SUM($S175:$V175)</f>
         <v>32</v>
       </c>
       <c r="S175">
@@ -37696,7 +37824,7 @@
         <v>3</v>
       </c>
       <c r="R176">
-        <f t="shared" si="2"/>
+        <f>SUM($S176:$V176)</f>
         <v>0</v>
       </c>
       <c r="S176" s="6">
@@ -37781,7 +37909,7 @@
         <v>3</v>
       </c>
       <c r="R177">
-        <f t="shared" si="2"/>
+        <f>SUM($S177:$V177)</f>
         <v>0</v>
       </c>
       <c r="S177" s="6">
@@ -37866,7 +37994,7 @@
         <v>3</v>
       </c>
       <c r="R178" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S178:$V178)</f>
         <v>34</v>
       </c>
       <c r="S178">
@@ -37950,7 +38078,7 @@
         <v>3</v>
       </c>
       <c r="R179">
-        <f t="shared" si="2"/>
+        <f>SUM($S179:$V179)</f>
         <v>0</v>
       </c>
       <c r="S179" s="6">
@@ -38035,7 +38163,7 @@
         <v>3</v>
       </c>
       <c r="R180">
-        <f t="shared" si="2"/>
+        <f>SUM($S180:$V180)</f>
         <v>0</v>
       </c>
       <c r="S180" s="6">
@@ -38120,7 +38248,7 @@
         <v>4</v>
       </c>
       <c r="R181" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S181:$V181)</f>
         <v>96</v>
       </c>
       <c r="S181">
@@ -38210,7 +38338,7 @@
         <v>3</v>
       </c>
       <c r="R182" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S182:$V182)</f>
         <v>39</v>
       </c>
       <c r="S182">
@@ -38294,7 +38422,7 @@
         <v>3</v>
       </c>
       <c r="R183">
-        <f t="shared" si="2"/>
+        <f>SUM($S183:$V183)</f>
         <v>0</v>
       </c>
       <c r="S183" s="6">
@@ -38379,7 +38507,7 @@
         <v>4</v>
       </c>
       <c r="R184">
-        <f t="shared" si="2"/>
+        <f>SUM($S184:$V184)</f>
         <v>82</v>
       </c>
       <c r="S184">
@@ -38469,7 +38597,7 @@
         <v>4</v>
       </c>
       <c r="R185" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S185:$V185)</f>
         <v>12</v>
       </c>
       <c r="S185">
@@ -38553,7 +38681,7 @@
         <v>3</v>
       </c>
       <c r="R186">
-        <f t="shared" si="2"/>
+        <f>SUM($S186:$V186)</f>
         <v>0</v>
       </c>
       <c r="S186" s="6">
@@ -38638,7 +38766,7 @@
         <v>3</v>
       </c>
       <c r="R187">
-        <f t="shared" si="2"/>
+        <f>SUM($S187:$V187)</f>
         <v>0</v>
       </c>
       <c r="S187" s="6">
@@ -38723,7 +38851,7 @@
         <v>3</v>
       </c>
       <c r="R188">
-        <f t="shared" si="2"/>
+        <f>SUM($S188:$V188)</f>
         <v>0</v>
       </c>
       <c r="S188" s="17">
@@ -38810,7 +38938,7 @@
         <v>4</v>
       </c>
       <c r="R189">
-        <f t="shared" si="2"/>
+        <f>SUM($S189:$V189)</f>
         <v>12</v>
       </c>
       <c r="S189" s="6">
@@ -38897,7 +39025,7 @@
         <v>3</v>
       </c>
       <c r="R190" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S190:$V190)</f>
         <v>48</v>
       </c>
       <c r="S190">
@@ -38981,7 +39109,7 @@
         <v>3</v>
       </c>
       <c r="R191" s="17">
-        <f t="shared" si="2"/>
+        <f>SUM($S191:$V191)</f>
         <v>0</v>
       </c>
       <c r="S191">
@@ -39068,7 +39196,7 @@
         <v>3</v>
       </c>
       <c r="R192">
-        <f t="shared" si="2"/>
+        <f>SUM($S192:$V192)</f>
         <v>0</v>
       </c>
       <c r="S192" s="6">
@@ -39156,7 +39284,7 @@
         <v>4</v>
       </c>
       <c r="R193">
-        <f t="shared" si="2"/>
+        <f>SUM($S193:$V193)</f>
         <v>0</v>
       </c>
       <c r="S193" s="9">
@@ -39243,7 +39371,7 @@
         <v>4</v>
       </c>
       <c r="R194" s="17">
-        <f t="shared" ref="R194:R223" si="3">SUM($S194:$V194)</f>
+        <f>SUM($S194:$V194)</f>
         <v>40</v>
       </c>
       <c r="S194">
@@ -39327,7 +39455,7 @@
         <v>3</v>
       </c>
       <c r="R195">
-        <f t="shared" si="3"/>
+        <f>SUM($S195:$V195)</f>
         <v>0</v>
       </c>
       <c r="S195" s="17">
@@ -39411,7 +39539,7 @@
         <v>4</v>
       </c>
       <c r="R196">
-        <f t="shared" si="3"/>
+        <f>SUM($S196:$V196)</f>
         <v>40</v>
       </c>
       <c r="S196">
@@ -39495,7 +39623,7 @@
         <v>3</v>
       </c>
       <c r="R197" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S197:$V197)</f>
         <v>0</v>
       </c>
       <c r="S197">
@@ -39579,7 +39707,7 @@
         <v>3</v>
       </c>
       <c r="R198" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S198:$V198)</f>
         <v>0</v>
       </c>
       <c r="S198">
@@ -39663,7 +39791,7 @@
         <v>3</v>
       </c>
       <c r="R199" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S199:$V199)</f>
         <v>0</v>
       </c>
       <c r="S199">
@@ -39747,7 +39875,7 @@
         <v>4</v>
       </c>
       <c r="R200" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S200:$V200)</f>
         <v>72</v>
       </c>
       <c r="S200">
@@ -39782,228 +39910,227 @@
       </c>
     </row>
     <row r="201" spans="1:29">
-      <c r="A201" s="28">
+      <c r="A201" s="3">
+        <v>11429</v>
+      </c>
+      <c r="B201" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C201" t="s">
+        <v>2997</v>
+      </c>
+      <c r="D201" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E201">
+        <v>39</v>
+      </c>
+      <c r="F201">
+        <v>37</v>
+      </c>
+      <c r="G201">
+        <v>80</v>
+      </c>
+      <c r="H201">
+        <v>37</v>
+      </c>
+      <c r="I201">
+        <v>95</v>
+      </c>
+      <c r="J201">
+        <v>128</v>
+      </c>
+      <c r="K201" s="1">
+        <v>93</v>
+      </c>
+      <c r="L201">
+        <v>82</v>
+      </c>
+      <c r="M201">
+        <v>47</v>
+      </c>
+      <c r="N201">
+        <v>36</v>
+      </c>
+      <c r="O201">
+        <v>1</v>
+      </c>
+      <c r="P201">
+        <v>27</v>
+      </c>
+      <c r="Q201">
+        <v>3</v>
+      </c>
+      <c r="R201" s="17">
+        <f>SUM($S201:$V201)</f>
+        <v>0</v>
+      </c>
+      <c r="S201">
+        <v>0</v>
+      </c>
+      <c r="T201">
+        <v>0</v>
+      </c>
+      <c r="U201">
+        <v>0</v>
+      </c>
+      <c r="V201">
+        <v>0</v>
+      </c>
+      <c r="W201">
+        <v>15</v>
+      </c>
+      <c r="X201">
+        <v>30</v>
+      </c>
+      <c r="Y201">
+        <v>0.6</v>
+      </c>
+      <c r="Z201">
+        <v>0.95</v>
+      </c>
+      <c r="AA201">
+        <v>114291</v>
+      </c>
+    </row>
+    <row r="202" spans="1:29">
+      <c r="A202" s="28">
         <v>11430</v>
       </c>
-      <c r="B201" t="s">
+      <c r="B202" t="s">
         <v>2354</v>
       </c>
-      <c r="C201" s="28" t="s">
+      <c r="C202" s="28" t="s">
         <v>2362</v>
       </c>
-      <c r="D201" t="s">
+      <c r="D202" t="s">
         <v>2044</v>
       </c>
-      <c r="E201">
+      <c r="E202">
         <v>52</v>
       </c>
-      <c r="F201">
+      <c r="F202">
         <v>61</v>
       </c>
-      <c r="G201">
-        <v>0</v>
-      </c>
-      <c r="H201">
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
         <v>58</v>
       </c>
-      <c r="I201">
+      <c r="I202">
         <v>105</v>
       </c>
-      <c r="J201">
-        <v>0</v>
-      </c>
-      <c r="K201" s="1">
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202" s="1">
         <v>99</v>
       </c>
-      <c r="L201">
+      <c r="L202">
         <v>74</v>
       </c>
-      <c r="M201">
+      <c r="M202">
         <v>44</v>
       </c>
-      <c r="N201">
+      <c r="N202">
         <v>33</v>
       </c>
-      <c r="O201">
+      <c r="O202">
         <v>2</v>
       </c>
-      <c r="P201">
+      <c r="P202">
         <v>17</v>
       </c>
-      <c r="Q201">
+      <c r="Q202">
         <v>4</v>
       </c>
-      <c r="R201" s="17">
-        <f t="shared" si="3"/>
+      <c r="R202" s="17">
+        <f>SUM($S202:$V202)</f>
         <v>48</v>
       </c>
-      <c r="S201">
+      <c r="S202">
         <v>12</v>
       </c>
-      <c r="T201">
+      <c r="T202">
         <v>12</v>
       </c>
-      <c r="U201">
+      <c r="U202">
         <v>12</v>
       </c>
-      <c r="V201">
+      <c r="V202">
         <v>12</v>
       </c>
-      <c r="W201">
+      <c r="W202">
         <v>30</v>
       </c>
-      <c r="X201">
+      <c r="X202">
         <v>75</v>
       </c>
-      <c r="Y201">
+      <c r="Y202">
         <v>0.9</v>
       </c>
-      <c r="Z201">
+      <c r="Z202">
         <v>1.7</v>
       </c>
-      <c r="AA201">
+      <c r="AA202">
         <v>114301</v>
       </c>
-    </row>
-    <row r="202" spans="1:29">
-      <c r="A202" s="3">
-        <v>11431</v>
-      </c>
-      <c r="B202" t="s">
-        <v>2055</v>
-      </c>
-      <c r="C202" t="s">
-        <v>2363</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>2011</v>
-      </c>
-      <c r="E202" s="6">
-        <v>60</v>
-      </c>
-      <c r="F202" s="6">
-        <v>65</v>
-      </c>
-      <c r="G202" s="6">
-        <v>60</v>
-      </c>
-      <c r="H202" s="6">
-        <v>47</v>
-      </c>
-      <c r="I202" s="6">
-        <v>81</v>
-      </c>
-      <c r="J202" s="6">
-        <v>0</v>
-      </c>
-      <c r="K202" s="10">
-        <v>97</v>
-      </c>
-      <c r="L202" s="6">
-        <v>84</v>
-      </c>
-      <c r="M202" s="6">
-        <v>62</v>
-      </c>
-      <c r="N202" s="6">
-        <v>31.5</v>
-      </c>
-      <c r="O202" s="6">
-        <v>2</v>
-      </c>
-      <c r="P202" s="6">
-        <v>20</v>
-      </c>
-      <c r="Q202" s="6">
-        <v>4</v>
-      </c>
-      <c r="R202">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S202" s="6">
-        <v>0</v>
-      </c>
-      <c r="T202" s="6">
-        <v>0</v>
-      </c>
-      <c r="U202" s="6">
-        <v>0</v>
-      </c>
-      <c r="V202" s="6">
-        <v>0</v>
-      </c>
-      <c r="W202" s="6">
-        <v>35</v>
-      </c>
-      <c r="X202" s="6">
-        <v>70</v>
-      </c>
-      <c r="Y202" s="6">
-        <v>1.28</v>
-      </c>
-      <c r="Z202" s="6">
-        <v>2.4</v>
-      </c>
-      <c r="AA202" s="6">
-        <v>114311</v>
-      </c>
-      <c r="AB202" s="6"/>
     </row>
     <row r="203" spans="1:29">
       <c r="A203" s="3">
-        <v>11456</v>
+        <v>11431</v>
       </c>
       <c r="B203" t="s">
-        <v>2102</v>
+        <v>2055</v>
       </c>
       <c r="C203" t="s">
-        <v>2364</v>
+        <v>2363</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>2044</v>
+        <v>2011</v>
       </c>
       <c r="E203" s="6">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F203" s="6">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G203" s="6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H203" s="6">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="I203" s="6">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="J203" s="6">
-        <v>79</v>
-      </c>
-      <c r="K203" s="6">
+        <v>0</v>
+      </c>
+      <c r="K203" s="10">
         <v>97</v>
       </c>
       <c r="L203" s="6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M203" s="6">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N203" s="6">
-        <v>32.6</v>
+        <v>31.5</v>
       </c>
       <c r="O203" s="6">
         <v>2</v>
       </c>
       <c r="P203" s="6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Q203" s="6">
         <v>4</v>
       </c>
       <c r="R203">
-        <f t="shared" si="3"/>
+        <f>SUM($S203:$V203)</f>
         <v>0</v>
       </c>
       <c r="S203" s="6">
@@ -40019,154 +40146,149 @@
         <v>0</v>
       </c>
       <c r="W203" s="6">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="X203" s="6">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="Y203" s="6">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="Z203" s="6">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="AA203" s="6">
-        <v>114561</v>
+        <v>114311</v>
       </c>
       <c r="AB203" s="6"/>
     </row>
     <row r="204" spans="1:29">
       <c r="A204" s="3">
-        <v>11467</v>
+        <v>11456</v>
       </c>
       <c r="B204" t="s">
-        <v>2076</v>
+        <v>2102</v>
       </c>
       <c r="C204" t="s">
-        <v>2123</v>
-      </c>
-      <c r="D204" t="s">
-        <v>2060</v>
-      </c>
-      <c r="E204">
-        <v>33</v>
-      </c>
-      <c r="F204">
-        <v>42</v>
-      </c>
-      <c r="G204">
-        <v>0</v>
-      </c>
-      <c r="H204">
-        <v>40</v>
-      </c>
-      <c r="I204">
-        <v>65</v>
-      </c>
-      <c r="J204">
-        <v>0</v>
-      </c>
-      <c r="K204" s="1">
-        <v>101</v>
-      </c>
-      <c r="L204">
-        <v>93</v>
-      </c>
-      <c r="M204">
-        <v>44</v>
-      </c>
-      <c r="N204">
-        <v>39</v>
-      </c>
-      <c r="O204">
-        <v>1</v>
-      </c>
-      <c r="P204">
-        <v>25</v>
-      </c>
-      <c r="Q204">
-        <v>3</v>
-      </c>
-      <c r="R204" s="17">
-        <f t="shared" si="3"/>
-        <v>24</v>
-      </c>
-      <c r="S204">
-        <v>8</v>
-      </c>
-      <c r="T204">
-        <v>8</v>
-      </c>
-      <c r="U204">
-        <v>8</v>
-      </c>
-      <c r="V204">
-        <v>0</v>
-      </c>
-      <c r="W204">
-        <v>25</v>
-      </c>
-      <c r="X204">
-        <v>65</v>
-      </c>
-      <c r="Y204">
-        <v>0.48</v>
-      </c>
-      <c r="Z204">
+        <v>2364</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E204" s="6">
+        <v>64</v>
+      </c>
+      <c r="F204" s="6">
+        <v>76</v>
+      </c>
+      <c r="G204" s="6">
+        <v>0</v>
+      </c>
+      <c r="H204" s="6">
+        <v>67</v>
+      </c>
+      <c r="I204" s="6">
+        <v>100</v>
+      </c>
+      <c r="J204" s="6">
+        <v>79</v>
+      </c>
+      <c r="K204" s="6">
+        <v>97</v>
+      </c>
+      <c r="L204" s="6">
+        <v>83</v>
+      </c>
+      <c r="M204" s="6">
+        <v>59</v>
+      </c>
+      <c r="N204" s="6">
+        <v>32.6</v>
+      </c>
+      <c r="O204" s="6">
+        <v>2</v>
+      </c>
+      <c r="P204" s="6">
+        <v>19</v>
+      </c>
+      <c r="Q204" s="6">
+        <v>4</v>
+      </c>
+      <c r="R204">
+        <f>SUM($S204:$V204)</f>
+        <v>0</v>
+      </c>
+      <c r="S204" s="6">
+        <v>0</v>
+      </c>
+      <c r="T204" s="6">
+        <v>0</v>
+      </c>
+      <c r="U204" s="6">
+        <v>0</v>
+      </c>
+      <c r="V204" s="6">
+        <v>0</v>
+      </c>
+      <c r="W204" s="6">
+        <v>45</v>
+      </c>
+      <c r="X204" s="6">
+        <v>80</v>
+      </c>
+      <c r="Y204" s="6">
         <v>1.5</v>
       </c>
-      <c r="AA204">
-        <v>104671</v>
-      </c>
-      <c r="AB204">
-        <v>114672</v>
-      </c>
-      <c r="AC204" s="3" t="s">
-        <v>2124</v>
-      </c>
+      <c r="Z204" s="6">
+        <v>2.8</v>
+      </c>
+      <c r="AA204" s="6">
+        <v>114561</v>
+      </c>
+      <c r="AB204" s="6"/>
     </row>
     <row r="205" spans="1:29">
       <c r="A205" s="3">
-        <v>11483</v>
+        <v>11467</v>
       </c>
       <c r="B205" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C205" s="7" t="s">
-        <v>2131</v>
+        <v>2076</v>
+      </c>
+      <c r="C205" t="s">
+        <v>2123</v>
       </c>
       <c r="D205" t="s">
-        <v>2011</v>
+        <v>2060</v>
       </c>
       <c r="E205">
-        <v>80</v>
+        <v>33</v>
       </c>
       <c r="F205">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G205">
         <v>0</v>
       </c>
       <c r="H205">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="I205">
+        <v>65</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205" s="1">
         <v>101</v>
       </c>
-      <c r="J205">
-        <v>0</v>
-      </c>
-      <c r="K205" s="1">
-        <v>97</v>
-      </c>
       <c r="L205">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="M205">
-        <v>78</v>
+        <v>44</v>
       </c>
       <c r="N205">
-        <v>30.5</v>
+        <v>39</v>
       </c>
       <c r="O205">
         <v>1</v>
@@ -40175,265 +40297,271 @@
         <v>25</v>
       </c>
       <c r="Q205">
-        <v>4</v>
-      </c>
-      <c r="R205">
-        <f t="shared" si="3"/>
-        <v>67</v>
+        <v>3</v>
+      </c>
+      <c r="R205" s="17">
+        <f>SUM($S205:$V205)</f>
+        <v>24</v>
       </c>
       <c r="S205">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T205">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="U205">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="V205">
-        <v>11</v>
-      </c>
-      <c r="W205" s="6">
-        <v>75</v>
-      </c>
-      <c r="X205" s="6">
-        <v>90</v>
-      </c>
-      <c r="Y205" s="6">
-        <v>2.88</v>
-      </c>
-      <c r="Z205" s="6">
-        <v>5.5</v>
+        <v>0</v>
+      </c>
+      <c r="W205">
+        <v>25</v>
+      </c>
+      <c r="X205">
+        <v>65</v>
+      </c>
+      <c r="Y205">
+        <v>0.48</v>
+      </c>
+      <c r="Z205">
+        <v>1.5</v>
       </c>
       <c r="AA205">
-        <v>104831</v>
-      </c>
-      <c r="AB205" s="6">
-        <v>114832</v>
+        <v>104671</v>
+      </c>
+      <c r="AB205">
+        <v>114672</v>
+      </c>
+      <c r="AC205" s="3" t="s">
+        <v>2124</v>
       </c>
     </row>
     <row r="206" spans="1:29">
       <c r="A206" s="3">
-        <v>11490</v>
+        <v>11483</v>
       </c>
       <c r="B206" t="s">
-        <v>2023</v>
-      </c>
-      <c r="C206" t="s">
-        <v>2134</v>
+        <v>2016</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>2131</v>
       </c>
       <c r="D206" t="s">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="E206">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="F206">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="G206">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H206">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="I206">
-        <v>70</v>
+        <v>101</v>
       </c>
       <c r="J206">
         <v>0</v>
       </c>
       <c r="K206" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L206">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="M206">
-        <v>44</v>
+        <v>78</v>
       </c>
       <c r="N206">
-        <v>35</v>
+        <v>30.5</v>
       </c>
       <c r="O206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P206">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="Q206">
         <v>4</v>
       </c>
-      <c r="R206" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
+      <c r="R206">
+        <f>SUM($S206:$V206)</f>
+        <v>67</v>
       </c>
       <c r="S206">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="T206">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="U206">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="V206">
-        <v>0</v>
-      </c>
-      <c r="W206">
+        <v>11</v>
+      </c>
+      <c r="W206" s="6">
+        <v>75</v>
+      </c>
+      <c r="X206" s="6">
+        <v>90</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>2.88</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>5.5</v>
+      </c>
+      <c r="AA206">
+        <v>104831</v>
+      </c>
+      <c r="AB206" s="6">
+        <v>114832</v>
+      </c>
+    </row>
+    <row r="207" spans="1:29">
+      <c r="A207" s="3">
+        <v>11490</v>
+      </c>
+      <c r="B207" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C207" t="s">
+        <v>2134</v>
+      </c>
+      <c r="D207" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E207">
+        <v>72</v>
+      </c>
+      <c r="F207">
+        <v>91</v>
+      </c>
+      <c r="G207">
+        <v>45</v>
+      </c>
+      <c r="H207">
+        <v>80</v>
+      </c>
+      <c r="I207">
+        <v>70</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207" s="1">
+        <v>94</v>
+      </c>
+      <c r="L207">
+        <v>73</v>
+      </c>
+      <c r="M207">
+        <v>44</v>
+      </c>
+      <c r="N207">
+        <v>35</v>
+      </c>
+      <c r="O207">
+        <v>3</v>
+      </c>
+      <c r="P207">
+        <v>6</v>
+      </c>
+      <c r="Q207">
+        <v>4</v>
+      </c>
+      <c r="R207" s="17">
+        <f>SUM($S207:$V207)</f>
+        <v>0</v>
+      </c>
+      <c r="S207">
+        <v>0</v>
+      </c>
+      <c r="T207">
+        <v>0</v>
+      </c>
+      <c r="U207">
+        <v>0</v>
+      </c>
+      <c r="V207">
+        <v>0</v>
+      </c>
+      <c r="W207">
         <v>60</v>
       </c>
-      <c r="X206">
+      <c r="X207">
         <v>130</v>
       </c>
-      <c r="Y206">
+      <c r="Y207">
         <v>2.8</v>
       </c>
-      <c r="Z206">
+      <c r="Z207">
         <v>5.8</v>
       </c>
-      <c r="AA206">
+      <c r="AA207">
         <v>104901</v>
       </c>
     </row>
-    <row r="207" spans="1:29">
-      <c r="A207" s="28">
+    <row r="208" spans="1:29">
+      <c r="A208" s="28">
         <v>11496</v>
-      </c>
-      <c r="B207" t="s">
-        <v>2228</v>
-      </c>
-      <c r="C207" s="28" t="s">
-        <v>2365</v>
-      </c>
-      <c r="D207" t="s">
-        <v>2006</v>
-      </c>
-      <c r="E207">
-        <v>43</v>
-      </c>
-      <c r="F207">
-        <v>46</v>
-      </c>
-      <c r="G207">
-        <v>83</v>
-      </c>
-      <c r="H207">
-        <v>42</v>
-      </c>
-      <c r="I207">
-        <v>95</v>
-      </c>
-      <c r="J207">
-        <v>136</v>
-      </c>
-      <c r="K207" s="1">
-        <v>92</v>
-      </c>
-      <c r="L207">
-        <v>91</v>
-      </c>
-      <c r="M207">
-        <v>51</v>
-      </c>
-      <c r="N207">
-        <v>32</v>
-      </c>
-      <c r="O207">
-        <v>1</v>
-      </c>
-      <c r="P207">
-        <v>10</v>
-      </c>
-      <c r="Q207">
-        <v>3</v>
-      </c>
-      <c r="R207" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S207">
-        <v>0</v>
-      </c>
-      <c r="T207">
-        <v>0</v>
-      </c>
-      <c r="U207">
-        <v>0</v>
-      </c>
-      <c r="V207">
-        <v>0</v>
-      </c>
-      <c r="W207">
-        <v>25</v>
-      </c>
-      <c r="X207">
-        <v>35</v>
-      </c>
-      <c r="Y207">
-        <v>0.7</v>
-      </c>
-      <c r="Z207">
-        <v>1.2</v>
-      </c>
-      <c r="AA207">
-        <v>114961</v>
-      </c>
-    </row>
-    <row r="208" spans="1:29">
-      <c r="A208" s="3">
-        <v>11503</v>
       </c>
       <c r="B208" t="s">
         <v>2228</v>
       </c>
-      <c r="C208" t="s">
-        <v>2366</v>
+      <c r="C208" s="28" t="s">
+        <v>2365</v>
       </c>
       <c r="D208" t="s">
-        <v>2019</v>
+        <v>2006</v>
       </c>
       <c r="E208">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F208">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G208">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H208">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="I208">
-        <v>65</v>
+        <v>95</v>
       </c>
       <c r="J208">
-        <v>71</v>
+        <v>136</v>
       </c>
       <c r="K208" s="1">
         <v>92</v>
       </c>
       <c r="L208">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="M208">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="N208">
-        <v>33.5</v>
+        <v>32</v>
       </c>
       <c r="O208">
         <v>1</v>
       </c>
       <c r="P208">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="Q208">
         <v>3</v>
       </c>
       <c r="R208" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S208:$V208)</f>
         <v>0</v>
       </c>
       <c r="S208">
@@ -40449,85 +40577,85 @@
         <v>0</v>
       </c>
       <c r="W208">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="X208">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="Y208">
-        <v>0.48</v>
+        <v>0.7</v>
       </c>
       <c r="Z208">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="AA208">
-        <v>115031</v>
+        <v>114961</v>
       </c>
     </row>
     <row r="209" spans="1:28">
       <c r="A209" s="3">
-        <v>11509</v>
+        <v>11503</v>
       </c>
       <c r="B209" t="s">
-        <v>2063</v>
+        <v>2228</v>
       </c>
       <c r="C209" t="s">
-        <v>2367</v>
+        <v>2366</v>
       </c>
       <c r="D209" t="s">
-        <v>2044</v>
+        <v>2019</v>
       </c>
       <c r="E209">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F209">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="H209">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="I209">
+        <v>65</v>
+      </c>
+      <c r="J209">
+        <v>71</v>
+      </c>
+      <c r="K209" s="1">
+        <v>92</v>
+      </c>
+      <c r="L209">
         <v>90</v>
       </c>
-      <c r="J209">
-        <v>74</v>
-      </c>
-      <c r="K209" s="1">
-        <v>107</v>
-      </c>
-      <c r="L209">
-        <v>85</v>
-      </c>
       <c r="M209">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="N209">
-        <v>34.5</v>
+        <v>33.5</v>
       </c>
       <c r="O209">
         <v>1</v>
       </c>
       <c r="P209">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="Q209">
         <v>3</v>
       </c>
       <c r="R209" s="17">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <f>SUM($S209:$V209)</f>
+        <v>0</v>
       </c>
       <c r="S209">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="T209">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="U209">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="V209">
         <v>0</v>
@@ -40536,156 +40664,156 @@
         <v>15</v>
       </c>
       <c r="X209">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="Y209">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="Z209">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AA209">
-        <v>115091</v>
+        <v>115031</v>
       </c>
     </row>
     <row r="210" spans="1:28">
-      <c r="A210" s="28">
-        <v>11516</v>
+      <c r="A210" s="3">
+        <v>11509</v>
       </c>
       <c r="B210" t="s">
-        <v>2102</v>
-      </c>
-      <c r="C210" s="28" t="s">
-        <v>2368</v>
+        <v>2063</v>
+      </c>
+      <c r="C210" t="s">
+        <v>2367</v>
       </c>
       <c r="D210" t="s">
         <v>2044</v>
       </c>
       <c r="E210">
+        <v>40</v>
+      </c>
+      <c r="F210">
+        <v>46</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>39</v>
+      </c>
+      <c r="I210">
+        <v>90</v>
+      </c>
+      <c r="J210">
+        <v>74</v>
+      </c>
+      <c r="K210" s="1">
+        <v>107</v>
+      </c>
+      <c r="L210">
+        <v>85</v>
+      </c>
+      <c r="M210">
+        <v>51</v>
+      </c>
+      <c r="N210">
+        <v>34.5</v>
+      </c>
+      <c r="O210">
+        <v>1</v>
+      </c>
+      <c r="P210">
+        <v>16</v>
+      </c>
+      <c r="Q210">
+        <v>3</v>
+      </c>
+      <c r="R210" s="17">
+        <f>SUM($S210:$V210)</f>
+        <v>48</v>
+      </c>
+      <c r="S210">
+        <v>16</v>
+      </c>
+      <c r="T210">
+        <v>16</v>
+      </c>
+      <c r="U210">
+        <v>16</v>
+      </c>
+      <c r="V210">
+        <v>0</v>
+      </c>
+      <c r="W210">
+        <v>15</v>
+      </c>
+      <c r="X210">
+        <v>40</v>
+      </c>
+      <c r="Y210">
+        <v>0.5</v>
+      </c>
+      <c r="Z210">
+        <v>0.9</v>
+      </c>
+      <c r="AA210">
+        <v>115091</v>
+      </c>
+    </row>
+    <row r="211" spans="1:28">
+      <c r="A211" s="28">
+        <v>11516</v>
+      </c>
+      <c r="B211" t="s">
+        <v>2102</v>
+      </c>
+      <c r="C211" s="28" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D211" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E211">
         <v>52</v>
       </c>
-      <c r="F210">
+      <c r="F211">
         <v>66</v>
       </c>
-      <c r="G210">
-        <v>0</v>
-      </c>
-      <c r="H210">
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
         <v>58</v>
       </c>
-      <c r="I210">
+      <c r="I211">
         <v>112</v>
       </c>
-      <c r="J210">
+      <c r="J211">
         <v>84</v>
       </c>
-      <c r="K210" s="1">
+      <c r="K211" s="1">
         <v>98</v>
       </c>
-      <c r="L210">
+      <c r="L211">
         <v>76</v>
       </c>
-      <c r="M210">
+      <c r="M211">
         <v>41</v>
-      </c>
-      <c r="N210">
-        <v>32</v>
-      </c>
-      <c r="O210">
-        <v>2</v>
-      </c>
-      <c r="P210">
-        <v>18</v>
-      </c>
-      <c r="Q210">
-        <v>4</v>
-      </c>
-      <c r="R210" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S210">
-        <v>0</v>
-      </c>
-      <c r="T210">
-        <v>0</v>
-      </c>
-      <c r="U210">
-        <v>0</v>
-      </c>
-      <c r="V210">
-        <v>0</v>
-      </c>
-      <c r="W210">
-        <v>25</v>
-      </c>
-      <c r="X210">
-        <v>45</v>
-      </c>
-      <c r="Y210">
-        <v>0.9</v>
-      </c>
-      <c r="Z210">
-        <v>1.6</v>
-      </c>
-      <c r="AA210">
-        <v>115161</v>
-      </c>
-    </row>
-    <row r="211" spans="1:28">
-      <c r="A211" s="3">
-        <v>11517</v>
-      </c>
-      <c r="B211" t="s">
-        <v>2228</v>
-      </c>
-      <c r="C211" t="s">
-        <v>2369</v>
-      </c>
-      <c r="D211" t="s">
-        <v>2019</v>
-      </c>
-      <c r="E211">
-        <v>36</v>
-      </c>
-      <c r="F211">
-        <v>40</v>
-      </c>
-      <c r="G211">
-        <v>75</v>
-      </c>
-      <c r="H211">
-        <v>37</v>
-      </c>
-      <c r="I211">
-        <v>89</v>
-      </c>
-      <c r="J211">
-        <v>128</v>
-      </c>
-      <c r="K211" s="1">
-        <v>92</v>
-      </c>
-      <c r="L211">
-        <v>90</v>
-      </c>
-      <c r="M211">
-        <v>37</v>
       </c>
       <c r="N211">
         <v>32</v>
       </c>
       <c r="O211">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P211">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q211">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R211" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S211:$V211)</f>
         <v>0</v>
       </c>
       <c r="S211">
@@ -40701,412 +40829,412 @@
         <v>0</v>
       </c>
       <c r="W211">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="X211">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="Y211">
-        <v>0.48</v>
+        <v>0.9</v>
       </c>
       <c r="Z211">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="AA211">
-        <v>115171</v>
+        <v>115161</v>
       </c>
     </row>
     <row r="212" spans="1:28">
       <c r="A212" s="3">
-        <v>11519</v>
+        <v>11517</v>
       </c>
       <c r="B212" t="s">
         <v>2228</v>
       </c>
       <c r="C212" t="s">
+        <v>2369</v>
+      </c>
+      <c r="D212" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E212">
+        <v>36</v>
+      </c>
+      <c r="F212">
+        <v>40</v>
+      </c>
+      <c r="G212">
+        <v>75</v>
+      </c>
+      <c r="H212">
+        <v>37</v>
+      </c>
+      <c r="I212">
+        <v>89</v>
+      </c>
+      <c r="J212">
+        <v>128</v>
+      </c>
+      <c r="K212" s="1">
+        <v>92</v>
+      </c>
+      <c r="L212">
+        <v>90</v>
+      </c>
+      <c r="M212">
+        <v>37</v>
+      </c>
+      <c r="N212">
+        <v>32</v>
+      </c>
+      <c r="O212">
+        <v>1</v>
+      </c>
+      <c r="P212">
+        <v>10</v>
+      </c>
+      <c r="Q212">
+        <v>3</v>
+      </c>
+      <c r="R212" s="17">
+        <f>SUM($S212:$V212)</f>
+        <v>0</v>
+      </c>
+      <c r="S212">
+        <v>0</v>
+      </c>
+      <c r="T212">
+        <v>0</v>
+      </c>
+      <c r="U212">
+        <v>0</v>
+      </c>
+      <c r="V212">
+        <v>0</v>
+      </c>
+      <c r="W212">
+        <v>15</v>
+      </c>
+      <c r="X212">
+        <v>25</v>
+      </c>
+      <c r="Y212">
+        <v>0.48</v>
+      </c>
+      <c r="Z212">
+        <v>0.9</v>
+      </c>
+      <c r="AA212">
+        <v>115171</v>
+      </c>
+    </row>
+    <row r="213" spans="1:28">
+      <c r="A213" s="3">
+        <v>11519</v>
+      </c>
+      <c r="B213" t="s">
+        <v>2228</v>
+      </c>
+      <c r="C213" t="s">
         <v>2370</v>
       </c>
-      <c r="D212" s="3" t="s">
+      <c r="D213" s="3" t="s">
         <v>2060</v>
       </c>
-      <c r="E212" s="6">
+      <c r="E213" s="6">
         <v>28</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F213" s="6">
         <v>32</v>
       </c>
-      <c r="G212" s="6">
+      <c r="G213" s="6">
         <v>73</v>
       </c>
-      <c r="H212" s="6">
+      <c r="H213" s="6">
         <v>33</v>
       </c>
-      <c r="I212" s="6">
+      <c r="I213" s="6">
         <v>46</v>
       </c>
-      <c r="J212" s="6">
+      <c r="J213" s="6">
         <v>57</v>
       </c>
-      <c r="K212" s="10">
+      <c r="K213" s="10">
         <v>93</v>
       </c>
-      <c r="L212" s="6">
+      <c r="L213" s="6">
         <v>92</v>
       </c>
-      <c r="M212" s="6">
+      <c r="M213" s="6">
         <v>40</v>
       </c>
-      <c r="N212" s="6">
+      <c r="N213" s="6">
         <v>30</v>
       </c>
-      <c r="O212" s="6">
-        <v>1</v>
-      </c>
-      <c r="P212" s="6">
+      <c r="O213" s="6">
+        <v>1</v>
+      </c>
+      <c r="P213" s="6">
         <v>6</v>
       </c>
-      <c r="Q212" s="6">
-        <v>3</v>
-      </c>
-      <c r="R212" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S212" s="6">
-        <v>0</v>
-      </c>
-      <c r="T212" s="6">
-        <v>0</v>
-      </c>
-      <c r="U212" s="6">
-        <v>0</v>
-      </c>
-      <c r="V212" s="6">
-        <v>0</v>
-      </c>
-      <c r="W212" s="6">
+      <c r="Q213" s="6">
+        <v>3</v>
+      </c>
+      <c r="R213" s="17">
+        <f>SUM($S213:$V213)</f>
+        <v>0</v>
+      </c>
+      <c r="S213" s="6">
+        <v>0</v>
+      </c>
+      <c r="T213" s="6">
+        <v>0</v>
+      </c>
+      <c r="U213" s="6">
+        <v>0</v>
+      </c>
+      <c r="V213" s="6">
+        <v>0</v>
+      </c>
+      <c r="W213" s="6">
         <v>10</v>
       </c>
-      <c r="X212" s="6">
+      <c r="X213" s="6">
         <v>15</v>
       </c>
-      <c r="Y212" s="6">
+      <c r="Y213" s="6">
         <v>0.45</v>
       </c>
-      <c r="Z212" s="6">
+      <c r="Z213" s="6">
         <v>0.8</v>
       </c>
-      <c r="AA212" s="6">
+      <c r="AA213" s="6">
         <v>115191</v>
       </c>
-      <c r="AB212" s="6"/>
-    </row>
-    <row r="213" spans="1:28">
-      <c r="A213" s="28">
+      <c r="AB213" s="6"/>
+    </row>
+    <row r="214" spans="1:28">
+      <c r="A214" s="28">
         <v>11527</v>
       </c>
-      <c r="B213" t="s">
+      <c r="B214" t="s">
         <v>2102</v>
       </c>
-      <c r="C213" s="28" t="s">
+      <c r="C214" s="28" t="s">
         <v>2371</v>
       </c>
-      <c r="D213" t="s">
+      <c r="D214" t="s">
         <v>2060</v>
       </c>
-      <c r="E213">
+      <c r="E214">
         <v>43</v>
       </c>
-      <c r="F213">
+      <c r="F214">
         <v>56</v>
       </c>
-      <c r="G213">
+      <c r="G214">
         <v>55</v>
       </c>
-      <c r="H213">
+      <c r="H214">
         <v>49</v>
       </c>
-      <c r="I213">
+      <c r="I214">
         <v>52</v>
       </c>
-      <c r="J213">
+      <c r="J214">
         <v>69</v>
       </c>
-      <c r="K213" s="1">
+      <c r="K214" s="1">
         <v>97</v>
       </c>
-      <c r="L213">
+      <c r="L214">
         <v>70</v>
       </c>
-      <c r="M213">
+      <c r="M214">
         <v>19</v>
       </c>
-      <c r="N213">
+      <c r="N214">
         <v>28</v>
-      </c>
-      <c r="O213">
-        <v>2</v>
-      </c>
-      <c r="P213">
-        <v>6</v>
-      </c>
-      <c r="Q213">
-        <v>3</v>
-      </c>
-      <c r="R213" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S213">
-        <v>0</v>
-      </c>
-      <c r="T213">
-        <v>0</v>
-      </c>
-      <c r="U213">
-        <v>0</v>
-      </c>
-      <c r="V213">
-        <v>0</v>
-      </c>
-      <c r="W213">
-        <v>25</v>
-      </c>
-      <c r="X213">
-        <v>25</v>
-      </c>
-      <c r="Y213">
-        <v>0.7</v>
-      </c>
-      <c r="Z213">
-        <v>1.3</v>
-      </c>
-      <c r="AA213">
-        <v>115271</v>
-      </c>
-    </row>
-    <row r="214" spans="1:28">
-      <c r="A214" s="3">
-        <v>11528</v>
-      </c>
-      <c r="B214" t="s">
-        <v>2354</v>
-      </c>
-      <c r="C214" s="28" t="s">
-        <v>2372</v>
-      </c>
-      <c r="D214" t="s">
-        <v>2006</v>
-      </c>
-      <c r="E214">
-        <v>60</v>
-      </c>
-      <c r="F214">
-        <v>61</v>
-      </c>
-      <c r="G214">
-        <v>0</v>
-      </c>
-      <c r="H214">
-        <v>68</v>
-      </c>
-      <c r="I214">
-        <v>112</v>
-      </c>
-      <c r="J214">
-        <v>0</v>
-      </c>
-      <c r="K214" s="1">
-        <v>99</v>
-      </c>
-      <c r="L214">
-        <v>85</v>
-      </c>
-      <c r="M214">
-        <v>54</v>
-      </c>
-      <c r="N214">
-        <v>33</v>
       </c>
       <c r="O214">
         <v>2</v>
       </c>
       <c r="P214">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="Q214">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R214" s="17">
-        <f t="shared" si="3"/>
-        <v>48</v>
+        <f>SUM($S214:$V214)</f>
+        <v>0</v>
       </c>
       <c r="S214">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T214">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U214">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V214">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="W214">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="X214">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="Y214">
-        <v>1.28</v>
+        <v>0.7</v>
       </c>
       <c r="Z214">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="AA214">
-        <v>115281</v>
+        <v>115271</v>
       </c>
     </row>
     <row r="215" spans="1:28">
       <c r="A215" s="3">
-        <v>11530</v>
+        <v>11528</v>
       </c>
       <c r="B215" t="s">
-        <v>2058</v>
-      </c>
-      <c r="C215" t="s">
-        <v>2373</v>
+        <v>2354</v>
+      </c>
+      <c r="C215" s="28" t="s">
+        <v>2372</v>
       </c>
       <c r="D215" t="s">
-        <v>2044</v>
+        <v>2006</v>
       </c>
       <c r="E215">
+        <v>60</v>
+      </c>
+      <c r="F215">
+        <v>61</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>68</v>
+      </c>
+      <c r="I215">
+        <v>112</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215" s="1">
+        <v>99</v>
+      </c>
+      <c r="L215">
+        <v>85</v>
+      </c>
+      <c r="M215">
+        <v>54</v>
+      </c>
+      <c r="N215">
+        <v>33</v>
+      </c>
+      <c r="O215">
+        <v>2</v>
+      </c>
+      <c r="P215">
+        <v>18</v>
+      </c>
+      <c r="Q215">
+        <v>4</v>
+      </c>
+      <c r="R215" s="17">
+        <f>SUM($S215:$V215)</f>
+        <v>48</v>
+      </c>
+      <c r="S215">
         <v>12</v>
       </c>
-      <c r="F215">
-        <v>23</v>
-      </c>
-      <c r="G215">
-        <v>73</v>
-      </c>
-      <c r="H215">
-        <v>30</v>
-      </c>
-      <c r="I215">
-        <v>0</v>
-      </c>
-      <c r="J215">
-        <v>0</v>
-      </c>
-      <c r="K215" s="1">
-        <v>108</v>
-      </c>
-      <c r="L215">
-        <v>78</v>
-      </c>
-      <c r="M215">
-        <v>52</v>
-      </c>
-      <c r="N215">
-        <v>16</v>
-      </c>
-      <c r="O215">
-        <v>1</v>
-      </c>
-      <c r="P215">
-        <v>15</v>
-      </c>
-      <c r="Q215">
-        <v>3</v>
-      </c>
-      <c r="R215" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="S215">
-        <v>0</v>
-      </c>
       <c r="T215">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U215">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V215">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="W215">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="X215">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="Y215">
-        <v>0.6</v>
+        <v>1.28</v>
       </c>
       <c r="Z215">
-        <v>0.65</v>
+        <v>2.4</v>
       </c>
       <c r="AA215">
-        <v>115301</v>
+        <v>115281</v>
       </c>
     </row>
     <row r="216" spans="1:28">
       <c r="A216" s="3">
-        <v>11532</v>
+        <v>11530</v>
       </c>
       <c r="B216" t="s">
-        <v>2009</v>
+        <v>2058</v>
       </c>
       <c r="C216" t="s">
-        <v>2149</v>
+        <v>2373</v>
       </c>
       <c r="D216" t="s">
-        <v>2040</v>
+        <v>2044</v>
       </c>
       <c r="E216">
-        <v>56</v>
+        <v>12</v>
       </c>
       <c r="F216">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="G216">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H216">
-        <v>84</v>
+        <v>30</v>
       </c>
       <c r="I216">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="J216">
         <v>0</v>
       </c>
       <c r="K216" s="1">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="L216">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="M216">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="N216">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="O216">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P216">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R216" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S216:$V216)</f>
         <v>0</v>
       </c>
       <c r="S216">
@@ -41122,78 +41250,75 @@
         <v>0</v>
       </c>
       <c r="W216">
-        <v>75</v>
+        <v>20</v>
       </c>
       <c r="X216">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="Y216">
-        <v>2.25</v>
+        <v>0.6</v>
       </c>
       <c r="Z216">
-        <v>4.5999999999999996</v>
+        <v>0.65</v>
       </c>
       <c r="AA216">
-        <v>105321</v>
-      </c>
-      <c r="AB216">
-        <v>115322</v>
+        <v>115301</v>
       </c>
     </row>
     <row r="217" spans="1:28">
       <c r="A217" s="3">
-        <v>11538</v>
+        <v>11532</v>
       </c>
       <c r="B217" t="s">
-        <v>2058</v>
+        <v>2009</v>
       </c>
       <c r="C217" t="s">
-        <v>2374</v>
+        <v>2149</v>
       </c>
       <c r="D217" t="s">
-        <v>2003</v>
+        <v>2040</v>
       </c>
       <c r="E217">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="F217">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="G217">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H217">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="I217">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="J217">
         <v>0</v>
       </c>
       <c r="K217" s="1">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="L217">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="M217">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="N217">
-        <v>23.6</v>
+        <v>22</v>
       </c>
       <c r="O217">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P217">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q217">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R217" s="17">
-        <f t="shared" si="3"/>
+        <f>SUM($S217:$V217)</f>
         <v>0</v>
       </c>
       <c r="S217">
@@ -41209,114 +41334,117 @@
         <v>0</v>
       </c>
       <c r="W217">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="X217">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="Y217">
-        <v>0.6</v>
+        <v>2.25</v>
       </c>
       <c r="Z217">
-        <v>0.7</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="AA217">
-        <v>115381</v>
+        <v>105321</v>
+      </c>
+      <c r="AB217">
+        <v>115322</v>
       </c>
     </row>
     <row r="218" spans="1:28">
       <c r="A218" s="3">
-        <v>11545</v>
+        <v>11538</v>
       </c>
       <c r="B218" t="s">
-        <v>2200</v>
+        <v>2058</v>
       </c>
       <c r="C218" t="s">
-        <v>2375</v>
+        <v>2374</v>
       </c>
       <c r="D218" t="s">
-        <v>2019</v>
+        <v>2003</v>
       </c>
       <c r="E218">
-        <v>68</v>
+        <v>21</v>
       </c>
       <c r="F218">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="G218">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H218">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="I218">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="J218">
         <v>0</v>
       </c>
       <c r="K218" s="1">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="L218">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="M218">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="N218">
-        <v>32</v>
+        <v>23.6</v>
       </c>
       <c r="O218">
         <v>1</v>
       </c>
       <c r="P218">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q218">
         <v>3</v>
       </c>
       <c r="R218" s="17">
-        <f t="shared" si="3"/>
-        <v>32</v>
+        <f>SUM($S218:$V218)</f>
+        <v>0</v>
       </c>
       <c r="S218">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T218">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="U218">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V218">
         <v>0</v>
       </c>
       <c r="W218">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="X218">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="Y218">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="Z218">
-        <v>2.64</v>
+        <v>0.7</v>
       </c>
       <c r="AA218">
-        <v>115451</v>
+        <v>115381</v>
       </c>
     </row>
     <row r="219" spans="1:28">
       <c r="A219" s="3">
-        <v>11560</v>
+        <v>11545</v>
       </c>
       <c r="B219" t="s">
-        <v>2225</v>
+        <v>2200</v>
       </c>
       <c r="C219" t="s">
-        <v>2376</v>
+        <v>2375</v>
       </c>
       <c r="D219" t="s">
         <v>2019</v>
@@ -41325,428 +41453,680 @@
         <v>68</v>
       </c>
       <c r="F219">
-        <v>74</v>
+        <v>40</v>
       </c>
       <c r="G219">
         <v>0</v>
       </c>
       <c r="H219">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="I219">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="J219">
         <v>0</v>
       </c>
       <c r="K219" s="1">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="L219">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="M219">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="N219">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="O219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P219">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="Q219">
         <v>3</v>
       </c>
       <c r="R219" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM($S219:$V219)</f>
+        <v>32</v>
       </c>
       <c r="S219">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T219">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="U219">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V219">
         <v>0</v>
       </c>
       <c r="W219">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="X219">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Y219">
         <v>1.3</v>
       </c>
       <c r="Z219">
-        <v>1.2</v>
+        <v>2.64</v>
       </c>
       <c r="AA219">
-        <v>115601</v>
+        <v>115451</v>
       </c>
     </row>
     <row r="220" spans="1:28">
       <c r="A220" s="3">
-        <v>11575</v>
+        <v>11560</v>
       </c>
       <c r="B220" t="s">
-        <v>2063</v>
+        <v>2225</v>
       </c>
       <c r="C220" t="s">
-        <v>2377</v>
+        <v>2376</v>
       </c>
       <c r="D220" t="s">
-        <v>2044</v>
+        <v>2019</v>
       </c>
       <c r="E220">
+        <v>68</v>
+      </c>
+      <c r="F220">
+        <v>74</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>74</v>
+      </c>
+      <c r="I220">
+        <v>60</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220" s="1">
+        <v>99</v>
+      </c>
+      <c r="L220">
+        <v>56</v>
+      </c>
+      <c r="M220">
+        <v>26</v>
+      </c>
+      <c r="N220">
+        <v>18</v>
+      </c>
+      <c r="O220">
+        <v>3</v>
+      </c>
+      <c r="P220">
+        <v>21</v>
+      </c>
+      <c r="Q220">
+        <v>3</v>
+      </c>
+      <c r="R220" s="17">
+        <f>SUM($S220:$V220)</f>
+        <v>0</v>
+      </c>
+      <c r="S220">
+        <v>0</v>
+      </c>
+      <c r="T220">
+        <v>0</v>
+      </c>
+      <c r="U220">
+        <v>0</v>
+      </c>
+      <c r="V220">
+        <v>0</v>
+      </c>
+      <c r="W220">
         <v>40</v>
       </c>
-      <c r="F220">
-        <v>46</v>
-      </c>
-      <c r="G220">
-        <v>0</v>
-      </c>
-      <c r="H220">
-        <v>39</v>
-      </c>
-      <c r="I220">
-        <v>94</v>
-      </c>
-      <c r="J220">
-        <v>74</v>
-      </c>
-      <c r="K220" s="1">
-        <v>107</v>
-      </c>
-      <c r="L220">
-        <v>86</v>
-      </c>
-      <c r="M220">
-        <v>48</v>
-      </c>
-      <c r="N220">
-        <v>35</v>
-      </c>
-      <c r="O220">
-        <v>1</v>
-      </c>
-      <c r="P220">
-        <v>17</v>
-      </c>
-      <c r="Q220">
-        <v>3</v>
-      </c>
-      <c r="R220" s="17">
-        <f t="shared" si="3"/>
-        <v>48</v>
-      </c>
-      <c r="S220">
-        <v>16</v>
-      </c>
-      <c r="T220">
-        <v>16</v>
-      </c>
-      <c r="U220">
-        <v>16</v>
-      </c>
-      <c r="V220">
-        <v>0</v>
-      </c>
-      <c r="W220">
-        <v>15</v>
-      </c>
       <c r="X220">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="Y220">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="Z220">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="AA220">
-        <v>115751</v>
+        <v>115601</v>
       </c>
     </row>
     <row r="221" spans="1:28">
       <c r="A221" s="3">
-        <v>11590</v>
+        <v>11575</v>
       </c>
       <c r="B221" t="s">
-        <v>2023</v>
+        <v>2063</v>
       </c>
       <c r="C221" t="s">
-        <v>2166</v>
+        <v>2377</v>
       </c>
       <c r="D221" t="s">
         <v>2044</v>
       </c>
       <c r="E221">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="F221">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="G221">
         <v>0</v>
       </c>
       <c r="H221">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="I221">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="J221">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="K221" s="1">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="L221">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="M221">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="N221">
-        <v>28.5</v>
+        <v>35</v>
       </c>
       <c r="O221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P221">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="Q221">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R221" s="17">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f>SUM($S221:$V221)</f>
+        <v>48</v>
       </c>
       <c r="S221">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="T221">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="U221">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V221">
         <v>0</v>
       </c>
       <c r="W221">
-        <v>75</v>
+        <v>15</v>
       </c>
       <c r="X221">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="Y221">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="Z221">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="AA221">
-        <v>105901</v>
-      </c>
-      <c r="AB221">
-        <v>115902</v>
+        <v>115751</v>
       </c>
     </row>
     <row r="222" spans="1:28">
       <c r="A222" s="3">
-        <v>11606</v>
+        <v>11583</v>
       </c>
       <c r="B222" t="s">
-        <v>2076</v>
+        <v>2999</v>
       </c>
       <c r="C222" t="s">
-        <v>2378</v>
+        <v>3000</v>
       </c>
       <c r="D222" t="s">
-        <v>2019</v>
+        <v>3001</v>
       </c>
       <c r="E222">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F222">
-        <v>45</v>
+        <v>95</v>
       </c>
       <c r="G222">
         <v>0</v>
       </c>
       <c r="H222">
-        <v>43</v>
+        <v>90</v>
       </c>
       <c r="I222">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="J222">
         <v>0</v>
       </c>
       <c r="K222" s="1">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="L222">
-        <v>97</v>
+        <v>51</v>
       </c>
       <c r="M222">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N222">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="O222">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P222">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="Q222">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R222" s="17">
-        <f t="shared" si="3"/>
-        <v>24</v>
+        <f>SUM($S222:$V222)</f>
+        <v>0</v>
       </c>
       <c r="S222">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T222">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="U222">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="V222">
         <v>0</v>
       </c>
       <c r="W222">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="X222">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="Y222">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="Z222">
-        <v>1</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="AA222">
-        <v>116061</v>
+        <v>115831</v>
       </c>
     </row>
     <row r="223" spans="1:28">
       <c r="A223" s="3">
+        <v>11589</v>
+      </c>
+      <c r="B223" t="s">
+        <v>2994</v>
+      </c>
+      <c r="C223" t="s">
+        <v>2995</v>
+      </c>
+      <c r="D223" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E223">
+        <v>37</v>
+      </c>
+      <c r="F223">
+        <v>43</v>
+      </c>
+      <c r="G223">
+        <v>88</v>
+      </c>
+      <c r="H223">
+        <v>40</v>
+      </c>
+      <c r="I223">
+        <v>91</v>
+      </c>
+      <c r="J223">
+        <v>84</v>
+      </c>
+      <c r="K223" s="1">
+        <v>94</v>
+      </c>
+      <c r="L223">
+        <v>93</v>
+      </c>
+      <c r="M223">
+        <v>37</v>
+      </c>
+      <c r="N223">
+        <v>38.5</v>
+      </c>
+      <c r="O223">
+        <v>1</v>
+      </c>
+      <c r="P223">
+        <v>25</v>
+      </c>
+      <c r="Q223">
+        <v>3</v>
+      </c>
+      <c r="R223" s="17">
+        <f>SUM($S223:$V223)</f>
+        <v>0</v>
+      </c>
+      <c r="S223">
+        <v>0</v>
+      </c>
+      <c r="T223">
+        <v>0</v>
+      </c>
+      <c r="U223">
+        <v>0</v>
+      </c>
+      <c r="V223">
+        <v>0</v>
+      </c>
+      <c r="W223">
+        <v>15</v>
+      </c>
+      <c r="X223">
+        <v>25</v>
+      </c>
+      <c r="Y223">
+        <v>0.48</v>
+      </c>
+      <c r="Z223">
+        <v>0.9</v>
+      </c>
+      <c r="AA223">
+        <v>115891</v>
+      </c>
+    </row>
+    <row r="224" spans="1:28">
+      <c r="A224" s="3">
+        <v>11590</v>
+      </c>
+      <c r="B224" t="s">
+        <v>2023</v>
+      </c>
+      <c r="C224" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D224" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E224">
+        <v>80</v>
+      </c>
+      <c r="F224">
+        <v>120</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>91</v>
+      </c>
+      <c r="I224">
+        <v>66</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224" s="1">
+        <v>100</v>
+      </c>
+      <c r="L224">
+        <v>72</v>
+      </c>
+      <c r="M224">
+        <v>44</v>
+      </c>
+      <c r="N224">
+        <v>28.5</v>
+      </c>
+      <c r="O224">
+        <v>3</v>
+      </c>
+      <c r="P224">
+        <v>9</v>
+      </c>
+      <c r="Q224">
+        <v>4</v>
+      </c>
+      <c r="R224" s="17">
+        <f>SUM($S224:$V224)</f>
+        <v>0</v>
+      </c>
+      <c r="S224">
+        <v>0</v>
+      </c>
+      <c r="T224">
+        <v>0</v>
+      </c>
+      <c r="U224">
+        <v>0</v>
+      </c>
+      <c r="V224">
+        <v>0</v>
+      </c>
+      <c r="W224">
+        <v>75</v>
+      </c>
+      <c r="X224">
+        <v>125</v>
+      </c>
+      <c r="Y224">
+        <v>2.8</v>
+      </c>
+      <c r="Z224">
+        <v>5</v>
+      </c>
+      <c r="AA224">
+        <v>105901</v>
+      </c>
+      <c r="AB224">
+        <v>115902</v>
+      </c>
+    </row>
+    <row r="225" spans="1:27">
+      <c r="A225" s="3">
+        <v>11606</v>
+      </c>
+      <c r="B225" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C225" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D225" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E225">
+        <v>43</v>
+      </c>
+      <c r="F225">
+        <v>45</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>43</v>
+      </c>
+      <c r="I225">
+        <v>97</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225" s="1">
+        <v>100</v>
+      </c>
+      <c r="L225">
+        <v>97</v>
+      </c>
+      <c r="M225">
+        <v>42</v>
+      </c>
+      <c r="N225">
+        <v>35</v>
+      </c>
+      <c r="O225">
+        <v>1</v>
+      </c>
+      <c r="P225">
+        <v>15</v>
+      </c>
+      <c r="Q225">
+        <v>3</v>
+      </c>
+      <c r="R225" s="17">
+        <f>SUM($S225:$V225)</f>
+        <v>24</v>
+      </c>
+      <c r="S225">
+        <v>8</v>
+      </c>
+      <c r="T225">
+        <v>8</v>
+      </c>
+      <c r="U225">
+        <v>8</v>
+      </c>
+      <c r="V225">
+        <v>0</v>
+      </c>
+      <c r="W225">
+        <v>30</v>
+      </c>
+      <c r="X225">
+        <v>60</v>
+      </c>
+      <c r="Y225">
+        <v>0.6</v>
+      </c>
+      <c r="Z225">
+        <v>1</v>
+      </c>
+      <c r="AA225">
+        <v>116061</v>
+      </c>
+    </row>
+    <row r="226" spans="1:27">
+      <c r="A226" s="3">
         <v>11618</v>
       </c>
-      <c r="B223" t="s">
+      <c r="B226" t="s">
         <v>2063</v>
       </c>
-      <c r="C223" t="s">
+      <c r="C226" t="s">
         <v>2379</v>
       </c>
-      <c r="D223" t="s">
+      <c r="D226" t="s">
         <v>2006</v>
       </c>
-      <c r="E223">
+      <c r="E226">
         <v>44</v>
       </c>
-      <c r="F223">
+      <c r="F226">
         <v>45</v>
       </c>
-      <c r="G223">
-        <v>0</v>
-      </c>
-      <c r="H223">
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
         <v>47</v>
       </c>
-      <c r="I223">
+      <c r="I226">
         <v>99</v>
       </c>
-      <c r="J223">
+      <c r="J226">
         <v>124</v>
       </c>
-      <c r="K223" s="1">
+      <c r="K226" s="1">
         <v>105</v>
       </c>
-      <c r="L223">
+      <c r="L226">
         <v>95</v>
       </c>
-      <c r="M223">
+      <c r="M226">
         <v>42</v>
       </c>
-      <c r="N223">
+      <c r="N226">
         <v>34</v>
       </c>
-      <c r="O223">
-        <v>1</v>
-      </c>
-      <c r="P223">
+      <c r="O226">
+        <v>1</v>
+      </c>
+      <c r="P226">
         <v>16</v>
       </c>
-      <c r="Q223">
-        <v>3</v>
-      </c>
-      <c r="R223" s="17">
-        <f t="shared" si="3"/>
+      <c r="Q226">
+        <v>3</v>
+      </c>
+      <c r="R226" s="17">
+        <f>SUM($S226:$V226)</f>
         <v>60</v>
       </c>
-      <c r="S223">
+      <c r="S226">
         <v>20</v>
       </c>
-      <c r="T223">
+      <c r="T226">
         <v>20</v>
       </c>
-      <c r="U223">
+      <c r="U226">
         <v>20</v>
       </c>
-      <c r="V223">
-        <v>0</v>
-      </c>
-      <c r="W223">
+      <c r="V226">
+        <v>0</v>
+      </c>
+      <c r="W226">
         <v>30</v>
       </c>
-      <c r="X223">
+      <c r="X226">
         <v>40</v>
       </c>
-      <c r="Y223">
+      <c r="Y226">
         <v>0.7</v>
       </c>
-      <c r="Z223">
+      <c r="Z226">
         <v>1.2</v>
       </c>
-      <c r="AA223">
+      <c r="AA226">
         <v>116181</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC206" xr:uid="{00000000-0009-0000-0000-000001000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC223">
-      <sortCondition ref="A1:A223"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AC226">
+      <sortCondition ref="A1:A226"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C2:C46">
-    <cfRule type="expression" dxfId="63" priority="81">
-      <formula>F2=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="62" priority="79">
+    <cfRule type="expression" dxfId="63" priority="79">
       <formula>F2=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="61" priority="80">
+    <cfRule type="expression" dxfId="62" priority="80">
       <formula>F2=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="61" priority="81">
+      <formula>F2=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="82">
       <formula>F2=3</formula>
@@ -41768,174 +42148,174 @@
     <cfRule type="expression" dxfId="55" priority="87">
       <formula>E47=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="90">
-      <formula>E47=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="53" priority="88">
+    <cfRule type="expression" dxfId="54" priority="88">
       <formula>E47=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="52" priority="89">
+    <cfRule type="expression" dxfId="53" priority="89">
       <formula>E47=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="52" priority="90">
+      <formula>E47=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C68">
-    <cfRule type="expression" dxfId="51" priority="72">
-      <formula>F60=1</formula>
+    <cfRule type="expression" dxfId="51" priority="67">
+      <formula>F60=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="71">
+    <cfRule type="expression" dxfId="50" priority="68">
+      <formula>F60=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="69">
+      <formula>F60=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="70">
+      <formula>F60=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="71">
       <formula>F60=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="70">
-      <formula>F60=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="69">
-      <formula>F60=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="68">
-      <formula>F60=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="67">
-      <formula>F60=6</formula>
+    <cfRule type="expression" dxfId="46" priority="72">
+      <formula>F60=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C83 C85">
     <cfRule type="expression" dxfId="45" priority="55">
       <formula>F82=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="60">
-      <formula>F82=1</formula>
+    <cfRule type="expression" dxfId="44" priority="56">
+      <formula>F82=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="59">
-      <formula>F82=2</formula>
+    <cfRule type="expression" dxfId="43" priority="57">
+      <formula>F82=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="58">
       <formula>F82=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="57">
-      <formula>F82=4</formula>
+    <cfRule type="expression" dxfId="41" priority="59">
+      <formula>F82=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="56">
-      <formula>F82=5</formula>
+    <cfRule type="expression" dxfId="40" priority="60">
+      <formula>F82=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C84">
-    <cfRule type="expression" dxfId="39" priority="64">
+    <cfRule type="expression" dxfId="39" priority="61">
+      <formula>F85=6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="62">
+      <formula>F85=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="37" priority="63">
+      <formula>F85=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="36" priority="64">
       <formula>F85=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="61">
-      <formula>F85=6</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="37" priority="66">
-      <formula>F85=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="36" priority="65">
+    <cfRule type="expression" dxfId="35" priority="65">
       <formula>F85=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="35" priority="63">
-      <formula>F85=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="62">
-      <formula>F85=5</formula>
+    <cfRule type="expression" dxfId="34" priority="66">
+      <formula>F85=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:C116">
-    <cfRule type="expression" dxfId="33" priority="32">
+    <cfRule type="expression" dxfId="33" priority="31">
+      <formula>F91=6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="32">
       <formula>F91=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="36">
-      <formula>F91=1</formula>
+    <cfRule type="expression" dxfId="31" priority="33">
+      <formula>F91=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="31" priority="35">
+    <cfRule type="expression" dxfId="30" priority="34">
+      <formula>F91=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="29" priority="35">
       <formula>F91=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="31">
-      <formula>F91=6</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="33">
-      <formula>F91=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="34">
-      <formula>F91=3</formula>
+    <cfRule type="expression" dxfId="28" priority="36">
+      <formula>F91=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C118">
     <cfRule type="expression" dxfId="27" priority="25">
       <formula>E117=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="30">
-      <formula>E117=1</formula>
+    <cfRule type="expression" dxfId="26" priority="26">
+      <formula>E117=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="29">
+    <cfRule type="expression" dxfId="25" priority="27">
+      <formula>E117=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="28">
+      <formula>E117=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="29">
       <formula>E117=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="26">
-      <formula>E117=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="23" priority="28">
-      <formula>E117=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="27">
-      <formula>E117=4</formula>
+    <cfRule type="expression" dxfId="22" priority="30">
+      <formula>E117=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C149:C151">
-    <cfRule type="expression" dxfId="21" priority="18">
-      <formula>F149=1</formula>
+    <cfRule type="expression" dxfId="21" priority="13">
+      <formula>F149=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="17">
+    <cfRule type="expression" dxfId="20" priority="14">
+      <formula>F149=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="15">
+      <formula>F149=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="16">
+      <formula>F149=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="17">
       <formula>F149=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="16">
-      <formula>F149=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="15">
-      <formula>F149=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="14">
-      <formula>F149=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="13">
-      <formula>F149=6</formula>
+    <cfRule type="expression" dxfId="16" priority="18">
+      <formula>F149=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C190">
-    <cfRule type="expression" dxfId="15" priority="12">
+    <cfRule type="expression" dxfId="15" priority="7">
+      <formula>F190=6</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="14" priority="8">
+      <formula>F190=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="9">
+      <formula>F190=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="10">
+      <formula>F190=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="11">
+      <formula>F190=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="10" priority="12">
       <formula>F190=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="11">
-      <formula>F190=1</formula>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C220:C226">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>F220=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="10">
-      <formula>F190=2</formula>
+    <cfRule type="expression" dxfId="8" priority="2">
+      <formula>F220=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="12" priority="9">
-      <formula>F190=3</formula>
+    <cfRule type="expression" dxfId="7" priority="3">
+      <formula>F220=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="11" priority="8">
-      <formula>F190=4</formula>
+    <cfRule type="expression" dxfId="6" priority="4">
+      <formula>F220=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="10" priority="7">
-      <formula>F190=6</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C220:C223">
-    <cfRule type="expression" dxfId="9" priority="6">
-      <formula>F220=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="8" priority="5">
+    <cfRule type="expression" dxfId="5" priority="5">
       <formula>F220=2</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="4">
-      <formula>F220=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="3">
-      <formula>F220=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
-      <formula>F220=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="1">
-      <formula>F220=6</formula>
+    <cfRule type="expression" dxfId="4" priority="6">
+      <formula>F220=1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/depend/ship/database.xlsx
+++ b/depend/ship/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/ship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53529017-5472-294F-8D28-CFDD9B3BE685}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599A9326-C5CA-2245-824C-F1C6759F5974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6320" yWindow="500" windowWidth="29400" windowHeight="19120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-41680" yWindow="-1620" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="舰船数据-未改" sheetId="1" r:id="rId1"/>
@@ -9343,6 +9343,241 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9933FF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0" tint="-0.34998626667073579"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF9900"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF808080"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFC000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF7030A0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF00B0F0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF65FF65"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF808080"/>
       </font>
     </dxf>
@@ -9358,62 +9593,7 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9933FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
       </font>
     </dxf>
     <dxf>
@@ -9448,11 +9628,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FFFFC000"/>
       </font>
     </dxf>
@@ -9463,12 +9638,17 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF808080"/>
+        <color rgb="FF7030A0"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF65FF65"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9933FF"/>
       </font>
     </dxf>
     <dxf>
@@ -9478,27 +9658,27 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFFC000"/>
+        <color theme="0" tint="-0.34998626667073579"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF9900"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF808080"/>
+        <color rgb="FFFF9900"/>
       </font>
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF65FF65"/>
+        <color rgb="FF9933FF"/>
       </font>
     </dxf>
     <dxf>
@@ -9508,192 +9688,12 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF808080"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF65FF65"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF7030A0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFC000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
+        <color rgb="FF00B050"/>
       </font>
     </dxf>
     <dxf>
       <font>
         <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9933FF"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF9900"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0" tint="-0.34998626667073579"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B050"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF00B0F0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9933FF"/>
       </font>
     </dxf>
     <dxf>
@@ -22665,40 +22665,40 @@
     <cfRule type="expression" dxfId="75" priority="7">
       <formula>F2=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="74" priority="8">
-      <formula>F2=4</formula>
+    <cfRule type="expression" dxfId="74" priority="11">
+      <formula>F2=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="73" priority="9">
+    <cfRule type="expression" dxfId="73" priority="10">
+      <formula>F2=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="72" priority="9">
       <formula>F2=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="72" priority="10">
-      <formula>F2=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="71" priority="11">
-      <formula>F2=1</formula>
+    <cfRule type="expression" dxfId="71" priority="8">
+      <formula>F2=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="70" priority="12">
       <formula>F2=5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C144">
-    <cfRule type="expression" dxfId="69" priority="1">
-      <formula>F144=6</formula>
+    <cfRule type="expression" dxfId="69" priority="6">
+      <formula>F144=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="68" priority="2">
+    <cfRule type="expression" dxfId="68" priority="5">
+      <formula>F144=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="67" priority="4">
+      <formula>F144=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="66" priority="3">
+      <formula>F144=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="65" priority="2">
       <formula>F144=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="67" priority="3">
-      <formula>F144=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="66" priority="4">
-      <formula>F144=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="65" priority="5">
-      <formula>F144=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="64" priority="6">
-      <formula>F144=5</formula>
+    <cfRule type="expression" dxfId="64" priority="1">
+      <formula>F144=6</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22858,7 +22858,7 @@
         <v>4</v>
       </c>
       <c r="R2">
-        <f>SUM($S2:$V2)</f>
+        <f t="shared" ref="R2:R65" si="0">SUM($S2:$V2)</f>
         <v>12</v>
       </c>
       <c r="S2" s="6">
@@ -22945,7 +22945,7 @@
         <v>4</v>
       </c>
       <c r="R3">
-        <f>SUM($S3:$V3)</f>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="S3">
@@ -23029,7 +23029,7 @@
         <v>4</v>
       </c>
       <c r="R4">
-        <f>SUM($S4:$V4)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="S4" s="9">
@@ -23114,7 +23114,7 @@
         <v>4</v>
       </c>
       <c r="R5">
-        <f>SUM($S5:$V5)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S5">
@@ -23198,7 +23198,7 @@
         <v>4</v>
       </c>
       <c r="R6">
-        <f>SUM($S6:$V6)</f>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="S6">
@@ -23282,7 +23282,7 @@
         <v>4</v>
       </c>
       <c r="R7">
-        <f>SUM($S7:$V7)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S7" s="9">
@@ -23369,7 +23369,7 @@
         <v>4</v>
       </c>
       <c r="R8">
-        <f>SUM($S8:$V8)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S8" s="9">
@@ -23454,7 +23454,7 @@
         <v>4</v>
       </c>
       <c r="R9">
-        <f>SUM($S9:$V9)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S9" s="9">
@@ -23542,7 +23542,7 @@
         <v>4</v>
       </c>
       <c r="R10">
-        <f>SUM($S10:$V10)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="S10" s="9">
@@ -23632,7 +23632,7 @@
         <v>4</v>
       </c>
       <c r="R11">
-        <f>SUM($S11:$V11)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S11" s="9">
@@ -23719,7 +23719,7 @@
         <v>4</v>
       </c>
       <c r="R12">
-        <f>SUM($S12:$V12)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S12" s="9">
@@ -23804,7 +23804,7 @@
         <v>4</v>
       </c>
       <c r="R13">
-        <f>SUM($S13:$V13)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S13" s="9">
@@ -23889,7 +23889,7 @@
         <v>4</v>
       </c>
       <c r="R14">
-        <f>SUM($S14:$V14)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S14" s="9">
@@ -23974,7 +23974,7 @@
         <v>4</v>
       </c>
       <c r="R15">
-        <f>SUM($S15:$V15)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S15" s="9">
@@ -24059,7 +24059,7 @@
         <v>4</v>
       </c>
       <c r="R16">
-        <f>SUM($S16:$V16)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S16" s="6">
@@ -24146,7 +24146,7 @@
         <v>4</v>
       </c>
       <c r="R17">
-        <f>SUM($S17:$V17)</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="S17" s="6">
@@ -24231,7 +24231,7 @@
         <v>4</v>
       </c>
       <c r="R18">
-        <f>SUM($S18:$V18)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="S18">
@@ -24315,7 +24315,7 @@
         <v>4</v>
       </c>
       <c r="R19">
-        <f>SUM($S19:$V19)</f>
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="S19">
@@ -24399,7 +24399,7 @@
         <v>4</v>
       </c>
       <c r="R20">
-        <f>SUM($S20:$V20)</f>
+        <f t="shared" si="0"/>
         <v>86</v>
       </c>
       <c r="S20">
@@ -24486,7 +24486,7 @@
         <v>4</v>
       </c>
       <c r="R21">
-        <f>SUM($S21:$V21)</f>
+        <f t="shared" si="0"/>
         <v>95</v>
       </c>
       <c r="S21">
@@ -24573,7 +24573,7 @@
         <v>3</v>
       </c>
       <c r="R22">
-        <f>SUM($S22:$V22)</f>
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="S22">
@@ -24657,7 +24657,7 @@
         <v>3</v>
       </c>
       <c r="R23">
-        <f>SUM($S23:$V23)</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="S23">
@@ -24741,7 +24741,7 @@
         <v>3</v>
       </c>
       <c r="R24">
-        <f>SUM($S24:$V24)</f>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="S24">
@@ -24822,7 +24822,7 @@
         <v>3</v>
       </c>
       <c r="R25">
-        <f>SUM($S25:$V25)</f>
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="S25">
@@ -24903,7 +24903,7 @@
         <v>4</v>
       </c>
       <c r="R26">
-        <f>SUM($S26:$V26)</f>
+        <f t="shared" si="0"/>
         <v>65</v>
       </c>
       <c r="S26">
@@ -24987,7 +24987,7 @@
         <v>4</v>
       </c>
       <c r="R27">
-        <f>SUM($S27:$V27)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="S27">
@@ -25071,7 +25071,7 @@
         <v>4</v>
       </c>
       <c r="R28">
-        <f>SUM($S28:$V28)</f>
+        <f t="shared" si="0"/>
         <v>85</v>
       </c>
       <c r="S28">
@@ -25158,7 +25158,7 @@
         <v>4</v>
       </c>
       <c r="R29">
-        <f>SUM($S29:$V29)</f>
+        <f t="shared" si="0"/>
         <v>87</v>
       </c>
       <c r="S29">
@@ -25242,7 +25242,7 @@
         <v>4</v>
       </c>
       <c r="R30">
-        <f>SUM($S30:$V30)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S30" s="6">
@@ -25327,7 +25327,7 @@
         <v>4</v>
       </c>
       <c r="R31">
-        <f>SUM($S31:$V31)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S31" s="6">
@@ -25412,7 +25412,7 @@
         <v>4</v>
       </c>
       <c r="R32">
-        <f>SUM($S32:$V32)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S32" s="6">
@@ -25497,7 +25497,7 @@
         <v>4</v>
       </c>
       <c r="R33">
-        <f>SUM($S33:$V33)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S33" s="6">
@@ -25582,7 +25582,7 @@
         <v>4</v>
       </c>
       <c r="R34">
-        <f>SUM($S34:$V34)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S34" s="6">
@@ -25667,7 +25667,7 @@
         <v>4</v>
       </c>
       <c r="R35">
-        <f>SUM($S35:$V35)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S35" s="6">
@@ -25752,7 +25752,7 @@
         <v>4</v>
       </c>
       <c r="R36">
-        <f>SUM($S36:$V36)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S36" s="6">
@@ -25839,7 +25839,7 @@
         <v>4</v>
       </c>
       <c r="R37">
-        <f>SUM($S37:$V37)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S37" s="6">
@@ -25924,7 +25924,7 @@
         <v>4</v>
       </c>
       <c r="R38">
-        <f>SUM($S38:$V38)</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="S38" s="6">
@@ -26011,7 +26011,7 @@
         <v>3</v>
       </c>
       <c r="R39" s="17">
-        <f>SUM($S39:$V39)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S39">
@@ -26098,7 +26098,7 @@
         <v>3</v>
       </c>
       <c r="R40" s="17">
-        <f>SUM($S40:$V40)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S40">
@@ -26185,7 +26185,7 @@
         <v>3</v>
       </c>
       <c r="R41" s="17">
-        <f>SUM($S41:$V41)</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="S41">
@@ -26269,7 +26269,7 @@
         <v>4</v>
       </c>
       <c r="R42" s="17">
-        <f>SUM($S42:$V42)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S42">
@@ -26353,7 +26353,7 @@
         <v>3</v>
       </c>
       <c r="R43">
-        <f>SUM($S43:$V43)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S43" s="6">
@@ -26438,7 +26438,7 @@
         <v>3</v>
       </c>
       <c r="R44">
-        <f>SUM($S44:$V44)</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="S44" s="6">
@@ -26523,7 +26523,7 @@
         <v>3</v>
       </c>
       <c r="R45">
-        <f>SUM($S45:$V45)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S45" s="6">
@@ -26611,7 +26611,7 @@
         <v>3</v>
       </c>
       <c r="R46">
-        <f>SUM($S46:$V46)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S46" s="6">
@@ -26699,7 +26699,7 @@
         <v>3</v>
       </c>
       <c r="R47">
-        <f>SUM($S47:$V47)</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="S47" s="6">
@@ -26786,7 +26786,7 @@
         <v>3</v>
       </c>
       <c r="R48" s="17">
-        <f>SUM($S48:$V48)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S48">
@@ -26870,7 +26870,7 @@
         <v>3</v>
       </c>
       <c r="R49" s="17">
-        <f>SUM($S49:$V49)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S49">
@@ -26954,7 +26954,7 @@
         <v>3</v>
       </c>
       <c r="R50">
-        <f>SUM($S50:$V50)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S50" s="6">
@@ -27044,7 +27044,7 @@
         <v>3</v>
       </c>
       <c r="R51">
-        <f>SUM($S51:$V51)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S51" s="6">
@@ -27132,7 +27132,7 @@
         <v>3</v>
       </c>
       <c r="R52">
-        <f>SUM($S52:$V52)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S52" s="6">
@@ -27220,7 +27220,7 @@
         <v>3</v>
       </c>
       <c r="R53">
-        <f>SUM($S53:$V53)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S53" s="6">
@@ -27308,7 +27308,7 @@
         <v>3</v>
       </c>
       <c r="R54">
-        <f>SUM($S54:$V54)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S54" s="6">
@@ -27396,7 +27396,7 @@
         <v>3</v>
       </c>
       <c r="R55">
-        <f>SUM($S55:$V55)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S55" s="6">
@@ -27484,7 +27484,7 @@
         <v>3</v>
       </c>
       <c r="R56">
-        <f>SUM($S56:$V56)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S56" s="6">
@@ -27572,7 +27572,7 @@
         <v>3</v>
       </c>
       <c r="R57">
-        <f>SUM($S57:$V57)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S57" s="6">
@@ -27660,7 +27660,7 @@
         <v>3</v>
       </c>
       <c r="R58">
-        <f>SUM($S58:$V58)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S58" s="6">
@@ -27748,7 +27748,7 @@
         <v>3</v>
       </c>
       <c r="R59">
-        <f>SUM($S59:$V59)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S59" s="6">
@@ -27836,7 +27836,7 @@
         <v>3</v>
       </c>
       <c r="R60">
-        <f>SUM($S60:$V60)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S60" s="6">
@@ -27924,7 +27924,7 @@
         <v>3</v>
       </c>
       <c r="R61">
-        <f>SUM($S61:$V61)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S61" s="6">
@@ -28014,7 +28014,7 @@
         <v>3</v>
       </c>
       <c r="R62">
-        <f>SUM($S62:$V62)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S62" s="6">
@@ -28102,7 +28102,7 @@
         <v>3</v>
       </c>
       <c r="R63">
-        <f>SUM($S63:$V63)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S63" s="6">
@@ -28190,7 +28190,7 @@
         <v>3</v>
       </c>
       <c r="R64">
-        <f>SUM($S64:$V64)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S64" s="6">
@@ -28278,7 +28278,7 @@
         <v>3</v>
       </c>
       <c r="R65">
-        <f>SUM($S65:$V65)</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="S65" s="6">
@@ -28366,7 +28366,7 @@
         <v>3</v>
       </c>
       <c r="R66">
-        <f>SUM($S66:$V66)</f>
+        <f t="shared" ref="R66:R129" si="1">SUM($S66:$V66)</f>
         <v>0</v>
       </c>
       <c r="S66" s="6">
@@ -28451,7 +28451,7 @@
         <v>3</v>
       </c>
       <c r="R67">
-        <f>SUM($S67:$V67)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S67" s="6">
@@ -28538,7 +28538,7 @@
         <v>3</v>
       </c>
       <c r="R68">
-        <f>SUM($S68:$V68)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S68" s="6">
@@ -28623,7 +28623,7 @@
         <v>3</v>
       </c>
       <c r="R69">
-        <f>SUM($S69:$V69)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S69" s="6">
@@ -28708,7 +28708,7 @@
         <v>3</v>
       </c>
       <c r="R70">
-        <f>SUM($S70:$V70)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S70" s="6">
@@ -28793,7 +28793,7 @@
         <v>3</v>
       </c>
       <c r="R71">
-        <f>SUM($S71:$V71)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S71" s="6">
@@ -28878,7 +28878,7 @@
         <v>3</v>
       </c>
       <c r="R72">
-        <f>SUM($S72:$V72)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S72" s="6">
@@ -28963,7 +28963,7 @@
         <v>3</v>
       </c>
       <c r="R73">
-        <f>SUM($S73:$V73)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S73" s="6">
@@ -29048,7 +29048,7 @@
         <v>3</v>
       </c>
       <c r="R74">
-        <f>SUM($S74:$V74)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S74" s="6">
@@ -29133,7 +29133,7 @@
         <v>3</v>
       </c>
       <c r="R75">
-        <f>SUM($S75:$V75)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S75" s="6">
@@ -29218,7 +29218,7 @@
         <v>3</v>
       </c>
       <c r="R76">
-        <f>SUM($S76:$V76)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S76" s="6">
@@ -29305,7 +29305,7 @@
         <v>3</v>
       </c>
       <c r="R77">
-        <f>SUM($S77:$V77)</f>
+        <f t="shared" si="1"/>
         <v>36</v>
       </c>
       <c r="S77">
@@ -29390,7 +29390,7 @@
         <v>3</v>
       </c>
       <c r="R78">
-        <f>SUM($S78:$V78)</f>
+        <f t="shared" si="1"/>
         <v>24</v>
       </c>
       <c r="S78">
@@ -29478,7 +29478,7 @@
         <v>3</v>
       </c>
       <c r="R79">
-        <f>SUM($S79:$V79)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S79" s="6">
@@ -29563,7 +29563,7 @@
         <v>3</v>
       </c>
       <c r="R80">
-        <f>SUM($S80:$V80)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S80" s="6">
@@ -29648,7 +29648,7 @@
         <v>4</v>
       </c>
       <c r="R81">
-        <f>SUM($S81:$V81)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S81" s="9">
@@ -29738,7 +29738,7 @@
         <v>4</v>
       </c>
       <c r="R82">
-        <f>SUM($S82:$V82)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S82" s="9">
@@ -29828,7 +29828,7 @@
         <v>4</v>
       </c>
       <c r="R83">
-        <f>SUM($S83:$V83)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S83" s="9">
@@ -29918,7 +29918,7 @@
         <v>4</v>
       </c>
       <c r="R84">
-        <f>SUM($S84:$V84)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S84" s="9">
@@ -30005,7 +30005,7 @@
         <v>4</v>
       </c>
       <c r="R85">
-        <f>SUM($S85:$V85)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S85" s="9">
@@ -30090,7 +30090,7 @@
         <v>4</v>
       </c>
       <c r="R86">
-        <f>SUM($S86:$V86)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S86" s="9">
@@ -30175,7 +30175,7 @@
         <v>4</v>
       </c>
       <c r="R87">
-        <f>SUM($S87:$V87)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S87" s="9">
@@ -30263,7 +30263,7 @@
         <v>4</v>
       </c>
       <c r="R88">
-        <f>SUM($S88:$V88)</f>
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="S88" s="9">
@@ -30353,7 +30353,7 @@
         <v>4</v>
       </c>
       <c r="R89">
-        <f>SUM($S89:$V89)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S89" s="9">
@@ -30443,7 +30443,7 @@
         <v>4</v>
       </c>
       <c r="R90">
-        <f>SUM($S90:$V90)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S90" s="9">
@@ -30530,7 +30530,7 @@
         <v>4</v>
       </c>
       <c r="R91">
-        <f>SUM($S91:$V91)</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="S91" s="9">
@@ -30618,7 +30618,7 @@
         <v>4</v>
       </c>
       <c r="R92">
-        <f>SUM($S92:$V92)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S92" s="9">
@@ -30705,7 +30705,7 @@
         <v>4</v>
       </c>
       <c r="R93">
-        <f>SUM($S93:$V93)</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="S93">
@@ -30792,7 +30792,7 @@
         <v>4</v>
       </c>
       <c r="R94">
-        <f>SUM($S94:$V94)</f>
+        <f t="shared" si="1"/>
         <v>68</v>
       </c>
       <c r="S94">
@@ -30877,7 +30877,7 @@
         <v>4</v>
       </c>
       <c r="R95">
-        <f>SUM($S95:$V95)</f>
+        <f t="shared" si="1"/>
         <v>83</v>
       </c>
       <c r="S95">
@@ -30962,7 +30962,7 @@
         <v>4</v>
       </c>
       <c r="R96">
-        <f>SUM($S96:$V96)</f>
+        <f t="shared" si="1"/>
         <v>90</v>
       </c>
       <c r="S96">
@@ -31049,7 +31049,7 @@
         <v>3</v>
       </c>
       <c r="R97">
-        <f>SUM($S97:$V97)</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="S97">
@@ -31134,7 +31134,7 @@
         <v>3</v>
       </c>
       <c r="R98">
-        <f>SUM($S98:$V98)</f>
+        <f t="shared" si="1"/>
         <v>32</v>
       </c>
       <c r="S98">
@@ -31219,7 +31219,7 @@
         <v>3</v>
       </c>
       <c r="R99">
-        <f>SUM($S99:$V99)</f>
+        <f t="shared" si="1"/>
         <v>46</v>
       </c>
       <c r="S99">
@@ -31304,7 +31304,7 @@
         <v>3</v>
       </c>
       <c r="R100">
-        <f>SUM($S100:$V100)</f>
+        <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="S100">
@@ -31389,7 +31389,7 @@
         <v>4</v>
       </c>
       <c r="R101">
-        <f>SUM($S101:$V101)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="S101" s="6">
@@ -31476,7 +31476,7 @@
         <v>4</v>
       </c>
       <c r="R102">
-        <f>SUM($S102:$V102)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="S102" s="6">
@@ -31561,7 +31561,7 @@
         <v>4</v>
       </c>
       <c r="R103">
-        <f>SUM($S103:$V103)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="S103" s="6">
@@ -31646,7 +31646,7 @@
         <v>4</v>
       </c>
       <c r="R104">
-        <f>SUM($S104:$V104)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="S104" s="6">
@@ -31731,7 +31731,7 @@
         <v>4</v>
       </c>
       <c r="R105">
-        <f>SUM($S105:$V105)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S105" s="6">
@@ -31816,7 +31816,7 @@
         <v>4</v>
       </c>
       <c r="R106">
-        <f>SUM($S106:$V106)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S106" s="6">
@@ -31901,7 +31901,7 @@
         <v>4</v>
       </c>
       <c r="R107">
-        <f>SUM($S107:$V107)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S107" s="6">
@@ -31986,7 +31986,7 @@
         <v>4</v>
       </c>
       <c r="R108">
-        <f>SUM($S108:$V108)</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="S108" s="6">
@@ -32071,7 +32071,7 @@
         <v>4</v>
       </c>
       <c r="R109">
-        <f>SUM($S109:$V109)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S109" s="6">
@@ -32156,7 +32156,7 @@
         <v>4</v>
       </c>
       <c r="R110">
-        <f>SUM($S110:$V110)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S110" s="6">
@@ -32241,7 +32241,7 @@
         <v>4</v>
       </c>
       <c r="R111">
-        <f>SUM($S111:$V111)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S111" s="6">
@@ -32326,7 +32326,7 @@
         <v>3</v>
       </c>
       <c r="R112" s="17">
-        <f>SUM($S112:$V112)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S112">
@@ -32413,7 +32413,7 @@
         <v>3</v>
       </c>
       <c r="R113">
-        <f>SUM($S113:$V113)</f>
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="S113" s="6">
@@ -32498,7 +32498,7 @@
         <v>3</v>
       </c>
       <c r="R114">
-        <f>SUM($S114:$V114)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S114" s="6">
@@ -32583,7 +32583,7 @@
         <v>3</v>
       </c>
       <c r="R115">
-        <f>SUM($S115:$V115)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S115" s="6">
@@ -32668,7 +32668,7 @@
         <v>3</v>
       </c>
       <c r="R116">
-        <f>SUM($S116:$V116)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S116" s="6">
@@ -32753,7 +32753,7 @@
         <v>3</v>
       </c>
       <c r="R117">
-        <f>SUM($S117:$V117)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S117" s="6">
@@ -32838,7 +32838,7 @@
         <v>3</v>
       </c>
       <c r="R118">
-        <f>SUM($S118:$V118)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S118" s="6">
@@ -32923,7 +32923,7 @@
         <v>3</v>
       </c>
       <c r="R119">
-        <f>SUM($S119:$V119)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S119" s="6">
@@ -33008,7 +33008,7 @@
         <v>3</v>
       </c>
       <c r="R120">
-        <f>SUM($S120:$V120)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S120" s="6">
@@ -33095,7 +33095,7 @@
         <v>3</v>
       </c>
       <c r="R121">
-        <f>SUM($S121:$V121)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S121" s="6">
@@ -33183,7 +33183,7 @@
         <v>3</v>
       </c>
       <c r="R122">
-        <f>SUM($S122:$V122)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S122" s="6">
@@ -33268,7 +33268,7 @@
         <v>3</v>
       </c>
       <c r="R123">
-        <f>SUM($S123:$V123)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S123" s="6">
@@ -33353,7 +33353,7 @@
         <v>3</v>
       </c>
       <c r="R124">
-        <f>SUM($S124:$V124)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S124" s="6">
@@ -33440,7 +33440,7 @@
         <v>3</v>
       </c>
       <c r="R125">
-        <f>SUM($S125:$V125)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S125" s="6">
@@ -33525,7 +33525,7 @@
         <v>3</v>
       </c>
       <c r="R126">
-        <f>SUM($S126:$V126)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S126" s="6">
@@ -33610,7 +33610,7 @@
         <v>3</v>
       </c>
       <c r="R127">
-        <f>SUM($S127:$V127)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S127" s="6">
@@ -33695,7 +33695,7 @@
         <v>3</v>
       </c>
       <c r="R128">
-        <f>SUM($S128:$V128)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S128" s="6">
@@ -33780,7 +33780,7 @@
         <v>3</v>
       </c>
       <c r="R129">
-        <f>SUM($S129:$V129)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="S129" s="6">
@@ -33865,7 +33865,7 @@
         <v>3</v>
       </c>
       <c r="R130">
-        <f>SUM($S130:$V130)</f>
+        <f t="shared" ref="R130:R193" si="2">SUM($S130:$V130)</f>
         <v>0</v>
       </c>
       <c r="S130" s="6">
@@ -33950,7 +33950,7 @@
         <v>3</v>
       </c>
       <c r="R131">
-        <f>SUM($S131:$V131)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S131" s="17">
@@ -34035,7 +34035,7 @@
         <v>3</v>
       </c>
       <c r="R132">
-        <f>SUM($S132:$V132)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S132" s="17">
@@ -34120,7 +34120,7 @@
         <v>3</v>
       </c>
       <c r="R133">
-        <f>SUM($S133:$V133)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S133" s="17">
@@ -34210,7 +34210,7 @@
         <v>3</v>
       </c>
       <c r="R134" s="17">
-        <f>SUM($S134:$V134)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S134">
@@ -34297,7 +34297,7 @@
         <v>3</v>
       </c>
       <c r="R135">
-        <f>SUM($S135:$V135)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S135">
@@ -34382,7 +34382,7 @@
         <v>4</v>
       </c>
       <c r="R136" s="17">
-        <f>SUM($S136:$V136)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S136">
@@ -34469,7 +34469,7 @@
         <v>4</v>
       </c>
       <c r="R137">
-        <f>SUM($S137:$V137)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S137" s="9">
@@ -34556,7 +34556,7 @@
         <v>4</v>
       </c>
       <c r="R138">
-        <f>SUM($S138:$V138)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S138" s="9">
@@ -34646,7 +34646,7 @@
         <v>4</v>
       </c>
       <c r="R139">
-        <f>SUM($S139:$V139)</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="S139">
@@ -34736,7 +34736,7 @@
         <v>4</v>
       </c>
       <c r="R140">
-        <f>SUM($S140:$V140)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S140" s="9">
@@ -34821,7 +34821,7 @@
         <v>4</v>
       </c>
       <c r="R141" s="17">
-        <f>SUM($S141:$V141)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S141">
@@ -34905,7 +34905,7 @@
         <v>4</v>
       </c>
       <c r="R142">
-        <f>SUM($S142:$V142)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="S142">
@@ -34990,7 +34990,7 @@
         <v>4</v>
       </c>
       <c r="R143">
-        <f>SUM($S143:$V143)</f>
+        <f t="shared" si="2"/>
         <v>87</v>
       </c>
       <c r="S143">
@@ -35075,7 +35075,7 @@
         <v>4</v>
       </c>
       <c r="R144">
-        <f>SUM($S144:$V144)</f>
+        <f t="shared" si="2"/>
         <v>73</v>
       </c>
       <c r="S144">
@@ -35162,7 +35162,7 @@
         <v>4</v>
       </c>
       <c r="R145">
-        <f>SUM($S145:$V145)</f>
+        <f t="shared" si="2"/>
         <v>70</v>
       </c>
       <c r="S145">
@@ -35247,7 +35247,7 @@
         <v>4</v>
       </c>
       <c r="R146">
-        <f>SUM($S146:$V146)</f>
+        <f t="shared" si="2"/>
         <v>72</v>
       </c>
       <c r="S146">
@@ -35334,7 +35334,7 @@
         <v>4</v>
       </c>
       <c r="R147">
-        <f>SUM($S147:$V147)</f>
+        <f t="shared" si="2"/>
         <v>69</v>
       </c>
       <c r="S147">
@@ -35421,7 +35421,7 @@
         <v>4</v>
       </c>
       <c r="R148">
-        <f>SUM($S148:$V148)</f>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="S148">
@@ -35506,7 +35506,7 @@
         <v>3</v>
       </c>
       <c r="R149">
-        <f>SUM($S149:$V149)</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="S149">
@@ -35591,7 +35591,7 @@
         <v>3</v>
       </c>
       <c r="R150">
-        <f>SUM($S150:$V150)</f>
+        <f t="shared" si="2"/>
         <v>55</v>
       </c>
       <c r="S150">
@@ -35676,7 +35676,7 @@
         <v>4</v>
       </c>
       <c r="R151" s="17">
-        <f>SUM($S151:$V151)</f>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="S151">
@@ -35760,7 +35760,7 @@
         <v>4</v>
       </c>
       <c r="R152">
-        <f>SUM($S152:$V152)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S152" s="6">
@@ -35845,7 +35845,7 @@
         <v>4</v>
       </c>
       <c r="R153" s="17">
-        <f>SUM($S153:$V153)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S153">
@@ -35929,7 +35929,7 @@
         <v>4</v>
       </c>
       <c r="R154" s="17">
-        <f>SUM($S154:$V154)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S154">
@@ -36013,7 +36013,7 @@
         <v>4</v>
       </c>
       <c r="R155">
-        <f>SUM($S155:$V155)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S155" s="6">
@@ -36098,7 +36098,7 @@
         <v>4</v>
       </c>
       <c r="R156">
-        <f>SUM($S156:$V156)</f>
+        <f t="shared" si="2"/>
         <v>8</v>
       </c>
       <c r="S156" s="6">
@@ -36185,7 +36185,7 @@
         <v>3</v>
       </c>
       <c r="R157" s="17">
-        <f>SUM($S157:$V157)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S157">
@@ -36269,7 +36269,7 @@
         <v>4</v>
       </c>
       <c r="R158">
-        <f>SUM($S158:$V158)</f>
+        <f t="shared" si="2"/>
         <v>18</v>
       </c>
       <c r="S158" s="6">
@@ -36354,7 +36354,7 @@
         <v>3</v>
       </c>
       <c r="R159" s="17">
-        <f>SUM($S159:$V159)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S159">
@@ -36438,7 +36438,7 @@
         <v>3</v>
       </c>
       <c r="R160">
-        <f>SUM($S160:$V160)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S160" s="6">
@@ -36523,7 +36523,7 @@
         <v>3</v>
       </c>
       <c r="R161" s="17">
-        <f>SUM($S161:$V161)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S161">
@@ -36610,7 +36610,7 @@
         <v>3</v>
       </c>
       <c r="R162" s="17">
-        <f>SUM($S162:$V162)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S162">
@@ -36694,7 +36694,7 @@
         <v>3</v>
       </c>
       <c r="R163">
-        <f>SUM($S163:$V163)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S163" s="6">
@@ -36782,7 +36782,7 @@
         <v>3</v>
       </c>
       <c r="R164">
-        <f>SUM($S164:$V164)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S164" s="6">
@@ -36870,7 +36870,7 @@
         <v>3</v>
       </c>
       <c r="R165" s="17">
-        <f>SUM($S165:$V165)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S165">
@@ -36954,7 +36954,7 @@
         <v>3</v>
       </c>
       <c r="R166" s="17">
-        <f>SUM($S166:$V166)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S166">
@@ -37041,7 +37041,7 @@
         <v>3</v>
       </c>
       <c r="R167" s="17">
-        <f>SUM($S167:$V167)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S167">
@@ -37128,7 +37128,7 @@
         <v>3</v>
       </c>
       <c r="R168">
-        <f>SUM($S168:$V168)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S168" s="6">
@@ -37215,7 +37215,7 @@
         <v>3</v>
       </c>
       <c r="R169">
-        <f>SUM($S169:$V169)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S169" s="6">
@@ -37302,7 +37302,7 @@
         <v>3</v>
       </c>
       <c r="R170">
-        <f>SUM($S170:$V170)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S170" s="6">
@@ -37389,7 +37389,7 @@
         <v>3</v>
       </c>
       <c r="R171">
-        <f>SUM($S171:$V171)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S171" s="17">
@@ -37476,7 +37476,7 @@
         <v>3</v>
       </c>
       <c r="R172">
-        <f>SUM($S172:$V172)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S172" s="17">
@@ -37563,7 +37563,7 @@
         <v>3</v>
       </c>
       <c r="R173" s="17">
-        <f>SUM($S173:$V173)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S173">
@@ -37650,7 +37650,7 @@
         <v>3</v>
       </c>
       <c r="R174">
-        <f>SUM($S174:$V174)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S174" s="17">
@@ -37737,7 +37737,7 @@
         <v>4</v>
       </c>
       <c r="R175">
-        <f>SUM($S175:$V175)</f>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="S175">
@@ -37824,7 +37824,7 @@
         <v>3</v>
       </c>
       <c r="R176">
-        <f>SUM($S176:$V176)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S176" s="6">
@@ -37909,7 +37909,7 @@
         <v>3</v>
       </c>
       <c r="R177">
-        <f>SUM($S177:$V177)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S177" s="6">
@@ -37994,7 +37994,7 @@
         <v>3</v>
       </c>
       <c r="R178" s="17">
-        <f>SUM($S178:$V178)</f>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="S178">
@@ -38078,7 +38078,7 @@
         <v>3</v>
       </c>
       <c r="R179">
-        <f>SUM($S179:$V179)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S179" s="6">
@@ -38163,7 +38163,7 @@
         <v>3</v>
       </c>
       <c r="R180">
-        <f>SUM($S180:$V180)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S180" s="6">
@@ -38248,7 +38248,7 @@
         <v>4</v>
       </c>
       <c r="R181" s="17">
-        <f>SUM($S181:$V181)</f>
+        <f t="shared" si="2"/>
         <v>96</v>
       </c>
       <c r="S181">
@@ -38338,7 +38338,7 @@
         <v>3</v>
       </c>
       <c r="R182" s="17">
-        <f>SUM($S182:$V182)</f>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="S182">
@@ -38422,7 +38422,7 @@
         <v>3</v>
       </c>
       <c r="R183">
-        <f>SUM($S183:$V183)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S183" s="6">
@@ -38507,7 +38507,7 @@
         <v>4</v>
       </c>
       <c r="R184">
-        <f>SUM($S184:$V184)</f>
+        <f t="shared" si="2"/>
         <v>82</v>
       </c>
       <c r="S184">
@@ -38597,7 +38597,7 @@
         <v>4</v>
       </c>
       <c r="R185" s="17">
-        <f>SUM($S185:$V185)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S185">
@@ -38681,7 +38681,7 @@
         <v>3</v>
       </c>
       <c r="R186">
-        <f>SUM($S186:$V186)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S186" s="6">
@@ -38766,7 +38766,7 @@
         <v>3</v>
       </c>
       <c r="R187">
-        <f>SUM($S187:$V187)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S187" s="6">
@@ -38851,7 +38851,7 @@
         <v>3</v>
       </c>
       <c r="R188">
-        <f>SUM($S188:$V188)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S188" s="17">
@@ -38938,7 +38938,7 @@
         <v>4</v>
       </c>
       <c r="R189">
-        <f>SUM($S189:$V189)</f>
+        <f t="shared" si="2"/>
         <v>12</v>
       </c>
       <c r="S189" s="6">
@@ -39025,7 +39025,7 @@
         <v>3</v>
       </c>
       <c r="R190" s="17">
-        <f>SUM($S190:$V190)</f>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="S190">
@@ -39109,7 +39109,7 @@
         <v>3</v>
       </c>
       <c r="R191" s="17">
-        <f>SUM($S191:$V191)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S191">
@@ -39196,7 +39196,7 @@
         <v>3</v>
       </c>
       <c r="R192">
-        <f>SUM($S192:$V192)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S192" s="6">
@@ -39284,7 +39284,7 @@
         <v>4</v>
       </c>
       <c r="R193">
-        <f>SUM($S193:$V193)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="S193" s="9">
@@ -39371,7 +39371,7 @@
         <v>4</v>
       </c>
       <c r="R194" s="17">
-        <f>SUM($S194:$V194)</f>
+        <f t="shared" ref="R194:R226" si="3">SUM($S194:$V194)</f>
         <v>40</v>
       </c>
       <c r="S194">
@@ -39455,7 +39455,7 @@
         <v>3</v>
       </c>
       <c r="R195">
-        <f>SUM($S195:$V195)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S195" s="17">
@@ -39539,7 +39539,7 @@
         <v>4</v>
       </c>
       <c r="R196">
-        <f>SUM($S196:$V196)</f>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="S196">
@@ -39623,7 +39623,7 @@
         <v>3</v>
       </c>
       <c r="R197" s="17">
-        <f>SUM($S197:$V197)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S197">
@@ -39707,7 +39707,7 @@
         <v>3</v>
       </c>
       <c r="R198" s="17">
-        <f>SUM($S198:$V198)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S198">
@@ -39791,7 +39791,7 @@
         <v>3</v>
       </c>
       <c r="R199" s="17">
-        <f>SUM($S199:$V199)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S199">
@@ -39875,7 +39875,7 @@
         <v>4</v>
       </c>
       <c r="R200" s="17">
-        <f>SUM($S200:$V200)</f>
+        <f t="shared" si="3"/>
         <v>72</v>
       </c>
       <c r="S200">
@@ -39941,7 +39941,7 @@
         <v>128</v>
       </c>
       <c r="K201" s="1">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="L201">
         <v>82</v>
@@ -39956,13 +39956,13 @@
         <v>1</v>
       </c>
       <c r="P201">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="Q201">
         <v>3</v>
       </c>
       <c r="R201" s="17">
-        <f>SUM($S201:$V201)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S201">
@@ -39984,10 +39984,10 @@
         <v>30</v>
       </c>
       <c r="Y201">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Z201">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AA201">
         <v>114291</v>
@@ -40046,7 +40046,7 @@
         <v>4</v>
       </c>
       <c r="R202" s="17">
-        <f>SUM($S202:$V202)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="S202">
@@ -40130,7 +40130,7 @@
         <v>4</v>
       </c>
       <c r="R203">
-        <f>SUM($S203:$V203)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S203" s="6">
@@ -40215,7 +40215,7 @@
         <v>4</v>
       </c>
       <c r="R204">
-        <f>SUM($S204:$V204)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S204" s="6">
@@ -40300,7 +40300,7 @@
         <v>3</v>
       </c>
       <c r="R205" s="17">
-        <f>SUM($S205:$V205)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="S205">
@@ -40390,7 +40390,7 @@
         <v>4</v>
       </c>
       <c r="R206">
-        <f>SUM($S206:$V206)</f>
+        <f t="shared" si="3"/>
         <v>67</v>
       </c>
       <c r="S206">
@@ -40477,7 +40477,7 @@
         <v>4</v>
       </c>
       <c r="R207" s="17">
-        <f>SUM($S207:$V207)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S207">
@@ -40561,7 +40561,7 @@
         <v>3</v>
       </c>
       <c r="R208" s="17">
-        <f>SUM($S208:$V208)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S208">
@@ -40645,7 +40645,7 @@
         <v>3</v>
       </c>
       <c r="R209" s="17">
-        <f>SUM($S209:$V209)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S209">
@@ -40729,7 +40729,7 @@
         <v>3</v>
       </c>
       <c r="R210" s="17">
-        <f>SUM($S210:$V210)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="S210">
@@ -40813,7 +40813,7 @@
         <v>4</v>
       </c>
       <c r="R211" s="17">
-        <f>SUM($S211:$V211)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S211">
@@ -40897,7 +40897,7 @@
         <v>3</v>
       </c>
       <c r="R212" s="17">
-        <f>SUM($S212:$V212)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S212">
@@ -40981,7 +40981,7 @@
         <v>3</v>
       </c>
       <c r="R213" s="17">
-        <f>SUM($S213:$V213)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S213" s="6">
@@ -41066,7 +41066,7 @@
         <v>3</v>
       </c>
       <c r="R214" s="17">
-        <f>SUM($S214:$V214)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S214">
@@ -41150,7 +41150,7 @@
         <v>4</v>
       </c>
       <c r="R215" s="17">
-        <f>SUM($S215:$V215)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="S215">
@@ -41234,7 +41234,7 @@
         <v>3</v>
       </c>
       <c r="R216" s="17">
-        <f>SUM($S216:$V216)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S216">
@@ -41318,7 +41318,7 @@
         <v>4</v>
       </c>
       <c r="R217" s="17">
-        <f>SUM($S217:$V217)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S217">
@@ -41405,7 +41405,7 @@
         <v>3</v>
       </c>
       <c r="R218" s="17">
-        <f>SUM($S218:$V218)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S218">
@@ -41489,7 +41489,7 @@
         <v>3</v>
       </c>
       <c r="R219" s="17">
-        <f>SUM($S219:$V219)</f>
+        <f t="shared" si="3"/>
         <v>32</v>
       </c>
       <c r="S219">
@@ -41573,7 +41573,7 @@
         <v>3</v>
       </c>
       <c r="R220" s="17">
-        <f>SUM($S220:$V220)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S220">
@@ -41657,7 +41657,7 @@
         <v>3</v>
       </c>
       <c r="R221" s="17">
-        <f>SUM($S221:$V221)</f>
+        <f t="shared" si="3"/>
         <v>48</v>
       </c>
       <c r="S221">
@@ -41720,7 +41720,7 @@
         <v>0</v>
       </c>
       <c r="K222" s="1">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L222">
         <v>51</v>
@@ -41735,13 +41735,13 @@
         <v>3</v>
       </c>
       <c r="P222">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Q222">
         <v>4</v>
       </c>
       <c r="R222" s="17">
-        <f>SUM($S222:$V222)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S222">
@@ -41792,19 +41792,19 @@
         <v>43</v>
       </c>
       <c r="G223">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H223">
         <v>40</v>
       </c>
       <c r="I223">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="J223">
         <v>84</v>
       </c>
       <c r="K223" s="1">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="L223">
         <v>93</v>
@@ -41819,13 +41819,13 @@
         <v>1</v>
       </c>
       <c r="P223">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="Q223">
         <v>3</v>
       </c>
       <c r="R223" s="17">
-        <f>SUM($S223:$V223)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S223">
@@ -41909,7 +41909,7 @@
         <v>4</v>
       </c>
       <c r="R224" s="17">
-        <f>SUM($S224:$V224)</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S224">
@@ -41996,7 +41996,7 @@
         <v>3</v>
       </c>
       <c r="R225" s="17">
-        <f>SUM($S225:$V225)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="S225">
@@ -42080,7 +42080,7 @@
         <v>3</v>
       </c>
       <c r="R226" s="17">
-        <f>SUM($S226:$V226)</f>
+        <f t="shared" si="3"/>
         <v>60</v>
       </c>
       <c r="S226">
@@ -42119,14 +42119,14 @@
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C2:C46">
-    <cfRule type="expression" dxfId="63" priority="79">
+    <cfRule type="expression" dxfId="63" priority="81">
+      <formula>F2=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="62" priority="79">
       <formula>F2=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="62" priority="80">
+    <cfRule type="expression" dxfId="61" priority="80">
       <formula>F2=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="61" priority="81">
-      <formula>F2=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="60" priority="82">
       <formula>F2=3</formula>
@@ -42148,174 +42148,174 @@
     <cfRule type="expression" dxfId="55" priority="87">
       <formula>E47=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="54" priority="88">
+    <cfRule type="expression" dxfId="54" priority="90">
+      <formula>E47=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="53" priority="88">
       <formula>E47=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="53" priority="89">
+    <cfRule type="expression" dxfId="52" priority="89">
       <formula>E47=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="52" priority="90">
-      <formula>E47=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C60:C68">
-    <cfRule type="expression" dxfId="51" priority="67">
-      <formula>F60=6</formula>
+    <cfRule type="expression" dxfId="51" priority="72">
+      <formula>F60=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="50" priority="68">
+    <cfRule type="expression" dxfId="50" priority="71">
+      <formula>F60=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="49" priority="70">
+      <formula>F60=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="48" priority="69">
+      <formula>F60=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="47" priority="68">
       <formula>F60=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="49" priority="69">
-      <formula>F60=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="48" priority="70">
-      <formula>F60=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="47" priority="71">
-      <formula>F60=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="46" priority="72">
-      <formula>F60=1</formula>
+    <cfRule type="expression" dxfId="46" priority="67">
+      <formula>F60=6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C82:C83 C85">
     <cfRule type="expression" dxfId="45" priority="55">
       <formula>F82=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="44" priority="56">
-      <formula>F82=5</formula>
+    <cfRule type="expression" dxfId="44" priority="60">
+      <formula>F82=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="43" priority="57">
-      <formula>F82=4</formula>
+    <cfRule type="expression" dxfId="43" priority="59">
+      <formula>F82=2</formula>
     </cfRule>
     <cfRule type="expression" dxfId="42" priority="58">
       <formula>F82=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="41" priority="59">
-      <formula>F82=2</formula>
+    <cfRule type="expression" dxfId="41" priority="57">
+      <formula>F82=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="40" priority="60">
-      <formula>F82=1</formula>
+    <cfRule type="expression" dxfId="40" priority="56">
+      <formula>F82=5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C84">
-    <cfRule type="expression" dxfId="39" priority="61">
+    <cfRule type="expression" dxfId="39" priority="64">
+      <formula>F85=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="38" priority="61">
       <formula>F85=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="38" priority="62">
-      <formula>F85=5</formula>
+    <cfRule type="expression" dxfId="37" priority="66">
+      <formula>F85=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="37" priority="63">
+    <cfRule type="expression" dxfId="36" priority="65">
+      <formula>F85=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="35" priority="63">
       <formula>F85=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="36" priority="64">
-      <formula>F85=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="35" priority="65">
-      <formula>F85=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="34" priority="66">
-      <formula>F85=1</formula>
+    <cfRule type="expression" dxfId="34" priority="62">
+      <formula>F85=5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C91:C116">
-    <cfRule type="expression" dxfId="33" priority="31">
+    <cfRule type="expression" dxfId="33" priority="32">
+      <formula>F91=5</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="32" priority="36">
+      <formula>F91=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="31" priority="35">
+      <formula>F91=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="30" priority="31">
       <formula>F91=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="32" priority="32">
-      <formula>F91=5</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="31" priority="33">
+    <cfRule type="expression" dxfId="29" priority="33">
       <formula>F91=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="34">
+    <cfRule type="expression" dxfId="28" priority="34">
       <formula>F91=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="29" priority="35">
-      <formula>F91=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="28" priority="36">
-      <formula>F91=1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C117:C118">
     <cfRule type="expression" dxfId="27" priority="25">
       <formula>E117=6</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="26" priority="26">
+    <cfRule type="expression" dxfId="26" priority="30">
+      <formula>E117=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="29">
+      <formula>E117=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="24" priority="26">
       <formula>E117=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="27">
-      <formula>E117=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="28">
+    <cfRule type="expression" dxfId="23" priority="28">
       <formula>E117=3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="29">
-      <formula>E117=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="22" priority="30">
-      <formula>E117=1</formula>
+    <cfRule type="expression" dxfId="22" priority="27">
+      <formula>E117=4</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C149:C151">
-    <cfRule type="expression" dxfId="21" priority="13">
-      <formula>F149=6</formula>
+    <cfRule type="expression" dxfId="21" priority="18">
+      <formula>F149=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="20" priority="14">
+    <cfRule type="expression" dxfId="20" priority="17">
+      <formula>F149=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="19" priority="16">
+      <formula>F149=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="18" priority="15">
+      <formula>F149=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="17" priority="14">
       <formula>F149=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="15">
-      <formula>F149=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="18" priority="16">
-      <formula>F149=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="17" priority="17">
-      <formula>F149=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="16" priority="18">
-      <formula>F149=1</formula>
+    <cfRule type="expression" dxfId="16" priority="13">
+      <formula>F149=6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C190">
-    <cfRule type="expression" dxfId="15" priority="7">
-      <formula>F190=6</formula>
+    <cfRule type="expression" dxfId="15" priority="12">
+      <formula>F190=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="8">
+    <cfRule type="expression" dxfId="14" priority="11">
+      <formula>F190=1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="13" priority="10">
+      <formula>F190=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="12" priority="9">
+      <formula>F190=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="11" priority="8">
       <formula>F190=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="9">
-      <formula>F190=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="12" priority="10">
-      <formula>F190=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="11">
-      <formula>F190=1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="10" priority="12">
-      <formula>F190=5</formula>
+    <cfRule type="expression" dxfId="10" priority="7">
+      <formula>F190=6</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C220:C226">
-    <cfRule type="expression" dxfId="9" priority="1">
-      <formula>F220=6</formula>
+    <cfRule type="expression" dxfId="9" priority="6">
+      <formula>F220=1</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="8" priority="2">
+    <cfRule type="expression" dxfId="8" priority="5">
+      <formula>F220=2</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="7" priority="4">
+      <formula>F220=3</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="6" priority="3">
+      <formula>F220=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>F220=5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="7" priority="3">
-      <formula>F220=4</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="6" priority="4">
-      <formula>F220=3</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="5">
-      <formula>F220=2</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="6">
-      <formula>F220=1</formula>
+    <cfRule type="expression" dxfId="4" priority="1">
+      <formula>F220=6</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/depend/ship/database.xlsx
+++ b/depend/ship/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/ship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599A9326-C5CA-2245-824C-F1C6759F5974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A319F2B-FB67-B149-A5EF-66AEB196EE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-41680" yWindow="-1620" windowWidth="29400" windowHeight="18380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-34940" yWindow="-1000" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="舰船数据-未改" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7465" uniqueCount="3002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7489" uniqueCount="3024">
   <si>
     <t>eid</t>
   </si>
@@ -9079,6 +9079,94 @@
   </si>
   <si>
     <t>I</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10761</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Torpedo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>550毫米三联鱼雷发射器</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鱼雷</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>F国舰船装备时提高20%伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country(F,{final_damage_buff:0.2})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10762</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MainGun</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>三联12英寸主炮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>主炮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中型船装备时提高30%伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShipType(MidShip,{final_damage_buff:0.3})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10763</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bomber</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>别-10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>轰炸机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S国舰船装备时增加20%命中率和10%伤害</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country(S,{hit_rate:0.2;final_damage_buff:0.1})</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10764</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>伊尔-2(白100号音乐家)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S国舰船装备时增加25%攻击威力和40点制空值</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Country(S,{power_buff:0.25;air_ctrl_buff:40})</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -42325,7 +42413,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AA779"/>
+  <dimension ref="A1:AA783"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2" customWidth="1"/>
@@ -65839,6 +65927,146 @@
       </c>
       <c r="AA779" s="2" t="s">
         <v>2986</v>
+      </c>
+    </row>
+    <row r="780" spans="1:27">
+      <c r="A780" s="2" t="s">
+        <v>3002</v>
+      </c>
+      <c r="B780" t="s">
+        <v>3003</v>
+      </c>
+      <c r="C780" t="s">
+        <v>3004</v>
+      </c>
+      <c r="D780" s="5" t="s">
+        <v>3005</v>
+      </c>
+      <c r="G780">
+        <v>12</v>
+      </c>
+      <c r="I780">
+        <v>10</v>
+      </c>
+      <c r="K780">
+        <v>3</v>
+      </c>
+      <c r="Q780">
+        <v>1</v>
+      </c>
+      <c r="Z780" t="s">
+        <v>3006</v>
+      </c>
+      <c r="AA780" s="2" t="s">
+        <v>3007</v>
+      </c>
+    </row>
+    <row r="781" spans="1:27">
+      <c r="A781" s="2" t="s">
+        <v>3008</v>
+      </c>
+      <c r="B781" t="s">
+        <v>3009</v>
+      </c>
+      <c r="C781" t="s">
+        <v>3010</v>
+      </c>
+      <c r="D781" s="5" t="s">
+        <v>3011</v>
+      </c>
+      <c r="F781">
+        <v>14</v>
+      </c>
+      <c r="K781">
+        <v>1</v>
+      </c>
+      <c r="L781">
+        <v>3</v>
+      </c>
+      <c r="Q781">
+        <v>1</v>
+      </c>
+      <c r="Z781" t="s">
+        <v>3012</v>
+      </c>
+      <c r="AA781" s="2" t="s">
+        <v>3013</v>
+      </c>
+    </row>
+    <row r="782" spans="1:27">
+      <c r="A782" s="2" t="s">
+        <v>3014</v>
+      </c>
+      <c r="B782" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C782" t="s">
+        <v>3016</v>
+      </c>
+      <c r="D782" s="5" t="s">
+        <v>3017</v>
+      </c>
+      <c r="I782">
+        <v>6</v>
+      </c>
+      <c r="K782">
+        <v>2</v>
+      </c>
+      <c r="O782">
+        <v>18</v>
+      </c>
+      <c r="Q782">
+        <v>1</v>
+      </c>
+      <c r="U782">
+        <v>10</v>
+      </c>
+      <c r="Z782" t="s">
+        <v>3018</v>
+      </c>
+      <c r="AA782" s="2" t="s">
+        <v>3019</v>
+      </c>
+    </row>
+    <row r="783" spans="1:27">
+      <c r="A783" s="2" t="s">
+        <v>3020</v>
+      </c>
+      <c r="B783" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C783" t="s">
+        <v>3021</v>
+      </c>
+      <c r="D783" s="5" t="s">
+        <v>3017</v>
+      </c>
+      <c r="F783">
+        <v>5</v>
+      </c>
+      <c r="K783">
+        <v>2</v>
+      </c>
+      <c r="M783">
+        <v>3</v>
+      </c>
+      <c r="N783">
+        <v>6</v>
+      </c>
+      <c r="O783">
+        <v>13</v>
+      </c>
+      <c r="Q783">
+        <v>1</v>
+      </c>
+      <c r="U783">
+        <v>5</v>
+      </c>
+      <c r="Z783" t="s">
+        <v>3022</v>
+      </c>
+      <c r="AA783" s="2" t="s">
+        <v>3023</v>
       </c>
     </row>
   </sheetData>
